--- a/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>49591000</v>
+        <v>49732700</v>
       </c>
       <c r="E8" s="3">
-        <v>49454300</v>
+        <v>49595600</v>
       </c>
       <c r="F8" s="3">
-        <v>47532800</v>
+        <v>47668600</v>
       </c>
       <c r="G8" s="3">
-        <v>48796800</v>
+        <v>48936200</v>
       </c>
       <c r="H8" s="3">
-        <v>47377600</v>
+        <v>47513000</v>
       </c>
       <c r="I8" s="3">
-        <v>50529500</v>
+        <v>50673900</v>
       </c>
       <c r="J8" s="3">
-        <v>51679600</v>
+        <v>51827300</v>
       </c>
       <c r="K8" s="3">
         <v>53640400</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>33472300</v>
+        <v>33567900</v>
       </c>
       <c r="E9" s="3">
-        <v>33172800</v>
+        <v>33267600</v>
       </c>
       <c r="F9" s="3">
-        <v>32643300</v>
+        <v>32736600</v>
       </c>
       <c r="G9" s="3">
-        <v>33290000</v>
+        <v>33385100</v>
       </c>
       <c r="H9" s="3">
-        <v>32723600</v>
+        <v>32817100</v>
       </c>
       <c r="I9" s="3">
-        <v>35556500</v>
+        <v>35658100</v>
       </c>
       <c r="J9" s="3">
-        <v>37515000</v>
+        <v>37622100</v>
       </c>
       <c r="K9" s="3">
         <v>39536200</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>16118800</v>
+        <v>16164800</v>
       </c>
       <c r="E10" s="3">
-        <v>16281500</v>
+        <v>16328000</v>
       </c>
       <c r="F10" s="3">
-        <v>14889500</v>
+        <v>14932000</v>
       </c>
       <c r="G10" s="3">
-        <v>15506800</v>
+        <v>15551100</v>
       </c>
       <c r="H10" s="3">
-        <v>14654000</v>
+        <v>14695900</v>
       </c>
       <c r="I10" s="3">
-        <v>14973000</v>
+        <v>15015800</v>
       </c>
       <c r="J10" s="3">
-        <v>14164700</v>
+        <v>14205100</v>
       </c>
       <c r="K10" s="3">
         <v>14104200</v>
@@ -951,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-9941900</v>
+        <v>-9970300</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -960,16 +960,16 @@
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <v>1828200</v>
+        <v>1833400</v>
       </c>
       <c r="H14" s="3">
-        <v>3824600</v>
+        <v>3835600</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>-1383400</v>
+        <v>-1387300</v>
       </c>
       <c r="K14" s="3">
         <v>612800</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>34079900</v>
+        <v>34177200</v>
       </c>
       <c r="E17" s="3">
-        <v>43147200</v>
+        <v>43270500</v>
       </c>
       <c r="F17" s="3">
-        <v>41967800</v>
+        <v>42087700</v>
       </c>
       <c r="G17" s="3">
-        <v>44349400</v>
+        <v>44476100</v>
       </c>
       <c r="H17" s="3">
-        <v>48409400</v>
+        <v>48547800</v>
       </c>
       <c r="I17" s="3">
-        <v>45865100</v>
+        <v>45996200</v>
       </c>
       <c r="J17" s="3">
-        <v>47638000</v>
+        <v>47774100</v>
       </c>
       <c r="K17" s="3">
         <v>52218900</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15511200</v>
+        <v>15555500</v>
       </c>
       <c r="E18" s="3">
-        <v>6307100</v>
+        <v>6325100</v>
       </c>
       <c r="F18" s="3">
-        <v>5565000</v>
+        <v>5580900</v>
       </c>
       <c r="G18" s="3">
-        <v>4447400</v>
+        <v>4460100</v>
       </c>
       <c r="H18" s="3">
-        <v>-1031800</v>
+        <v>-1034800</v>
       </c>
       <c r="I18" s="3">
-        <v>4664400</v>
+        <v>4677700</v>
       </c>
       <c r="J18" s="3">
-        <v>4041600</v>
+        <v>4053200</v>
       </c>
       <c r="K18" s="3">
         <v>1421500</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1190200</v>
+        <v>1193600</v>
       </c>
       <c r="E20" s="3">
-        <v>762800</v>
+        <v>764900</v>
       </c>
       <c r="F20" s="3">
-        <v>1928000</v>
+        <v>1933600</v>
       </c>
       <c r="G20" s="3">
-        <v>-583700</v>
+        <v>-585400</v>
       </c>
       <c r="H20" s="3">
-        <v>-51000</v>
+        <v>-51100</v>
       </c>
       <c r="I20" s="3">
-        <v>731300</v>
+        <v>733400</v>
       </c>
       <c r="J20" s="3">
-        <v>279900</v>
+        <v>280700</v>
       </c>
       <c r="K20" s="3">
         <v>-596600</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>31471500</v>
+        <v>31655200</v>
       </c>
       <c r="E21" s="3">
-        <v>22086100</v>
+        <v>22244700</v>
       </c>
       <c r="F21" s="3">
-        <v>22787000</v>
+        <v>22949200</v>
       </c>
       <c r="G21" s="3">
-        <v>19236800</v>
+        <v>19389400</v>
       </c>
       <c r="H21" s="3">
-        <v>9540800</v>
+        <v>9635600</v>
       </c>
       <c r="I21" s="3">
-        <v>16685300</v>
+        <v>16804700</v>
       </c>
       <c r="J21" s="3">
-        <v>16345400</v>
+        <v>16468500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>8</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2796000</v>
+        <v>2804000</v>
       </c>
       <c r="E22" s="3">
-        <v>2618100</v>
+        <v>2625600</v>
       </c>
       <c r="F22" s="3">
-        <v>2776500</v>
+        <v>2784400</v>
       </c>
       <c r="G22" s="3">
-        <v>3001100</v>
+        <v>3009700</v>
       </c>
       <c r="H22" s="3">
-        <v>1752300</v>
+        <v>1757300</v>
       </c>
       <c r="I22" s="3">
-        <v>1188100</v>
+        <v>1191500</v>
       </c>
       <c r="J22" s="3">
-        <v>1292200</v>
+        <v>1295900</v>
       </c>
       <c r="K22" s="3">
         <v>1029500</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>13905400</v>
+        <v>13945100</v>
       </c>
       <c r="E23" s="3">
-        <v>4451800</v>
+        <v>4464500</v>
       </c>
       <c r="F23" s="3">
-        <v>4716500</v>
+        <v>4730000</v>
       </c>
       <c r="G23" s="3">
-        <v>862600</v>
+        <v>865000</v>
       </c>
       <c r="H23" s="3">
-        <v>-2835100</v>
+        <v>-2843200</v>
       </c>
       <c r="I23" s="3">
-        <v>4207600</v>
+        <v>4219700</v>
       </c>
       <c r="J23" s="3">
-        <v>3029300</v>
+        <v>3038000</v>
       </c>
       <c r="K23" s="3">
         <v>-204600</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>521900</v>
+        <v>523400</v>
       </c>
       <c r="E24" s="3">
-        <v>1443100</v>
+        <v>1447200</v>
       </c>
       <c r="F24" s="3">
-        <v>4192400</v>
+        <v>4204400</v>
       </c>
       <c r="G24" s="3">
-        <v>1356300</v>
+        <v>1360100</v>
       </c>
       <c r="H24" s="3">
-        <v>1623200</v>
+        <v>1627800</v>
       </c>
       <c r="I24" s="3">
-        <v>-953700</v>
+        <v>-956400</v>
       </c>
       <c r="J24" s="3">
-        <v>5168900</v>
+        <v>5183700</v>
       </c>
       <c r="K24" s="3">
         <v>5316700</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>13383500</v>
+        <v>13421700</v>
       </c>
       <c r="E26" s="3">
-        <v>3008700</v>
+        <v>3017300</v>
       </c>
       <c r="F26" s="3">
-        <v>524100</v>
+        <v>525600</v>
       </c>
       <c r="G26" s="3">
-        <v>-493700</v>
+        <v>-495100</v>
       </c>
       <c r="H26" s="3">
-        <v>-4458300</v>
+        <v>-4471000</v>
       </c>
       <c r="I26" s="3">
-        <v>5161300</v>
+        <v>5176100</v>
       </c>
       <c r="J26" s="3">
-        <v>-2139600</v>
+        <v>-2145700</v>
       </c>
       <c r="K26" s="3">
         <v>-5521300</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12844200</v>
+        <v>12880900</v>
       </c>
       <c r="E27" s="3">
-        <v>2427100</v>
+        <v>2434100</v>
       </c>
       <c r="F27" s="3">
-        <v>64000</v>
+        <v>64200</v>
       </c>
       <c r="G27" s="3">
-        <v>-998200</v>
+        <v>-1001100</v>
       </c>
       <c r="H27" s="3">
-        <v>-4866200</v>
+        <v>-4880100</v>
       </c>
       <c r="I27" s="3">
-        <v>4782700</v>
+        <v>4796300</v>
       </c>
       <c r="J27" s="3">
-        <v>-2376200</v>
+        <v>-2382900</v>
       </c>
       <c r="K27" s="3">
         <v>-5826000</v>
@@ -1542,13 +1542,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-3835500</v>
+        <v>-3846400</v>
       </c>
       <c r="I29" s="3">
-        <v>-2136400</v>
+        <v>-2142500</v>
       </c>
       <c r="J29" s="3">
-        <v>-4456100</v>
+        <v>-4468800</v>
       </c>
       <c r="K29" s="3">
         <v>5400</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1190200</v>
+        <v>-1193600</v>
       </c>
       <c r="E32" s="3">
-        <v>-762800</v>
+        <v>-764900</v>
       </c>
       <c r="F32" s="3">
-        <v>-1928000</v>
+        <v>-1933600</v>
       </c>
       <c r="G32" s="3">
-        <v>583700</v>
+        <v>585400</v>
       </c>
       <c r="H32" s="3">
-        <v>51000</v>
+        <v>51100</v>
       </c>
       <c r="I32" s="3">
-        <v>-731300</v>
+        <v>-733400</v>
       </c>
       <c r="J32" s="3">
-        <v>-279900</v>
+        <v>-280700</v>
       </c>
       <c r="K32" s="3">
         <v>596600</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12844200</v>
+        <v>12880900</v>
       </c>
       <c r="E33" s="3">
-        <v>2427100</v>
+        <v>2434100</v>
       </c>
       <c r="F33" s="3">
-        <v>64000</v>
+        <v>64200</v>
       </c>
       <c r="G33" s="3">
-        <v>-998200</v>
+        <v>-1001100</v>
       </c>
       <c r="H33" s="3">
-        <v>-8701700</v>
+        <v>-8726600</v>
       </c>
       <c r="I33" s="3">
-        <v>2646300</v>
+        <v>2653900</v>
       </c>
       <c r="J33" s="3">
-        <v>-6832200</v>
+        <v>-6851800</v>
       </c>
       <c r="K33" s="3">
         <v>-5820600</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12844200</v>
+        <v>12880900</v>
       </c>
       <c r="E35" s="3">
-        <v>2427100</v>
+        <v>2434100</v>
       </c>
       <c r="F35" s="3">
-        <v>64000</v>
+        <v>64200</v>
       </c>
       <c r="G35" s="3">
-        <v>-998200</v>
+        <v>-1001100</v>
       </c>
       <c r="H35" s="3">
-        <v>-8701700</v>
+        <v>-8726600</v>
       </c>
       <c r="I35" s="3">
-        <v>2646300</v>
+        <v>2653900</v>
       </c>
       <c r="J35" s="3">
-        <v>-6832200</v>
+        <v>-6851800</v>
       </c>
       <c r="K35" s="3">
         <v>-5820600</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>10801200</v>
+        <v>10832000</v>
       </c>
       <c r="E41" s="3">
-        <v>10541900</v>
+        <v>10572000</v>
       </c>
       <c r="F41" s="3">
-        <v>6315800</v>
+        <v>6333800</v>
       </c>
       <c r="G41" s="3">
-        <v>12320200</v>
+        <v>12355400</v>
       </c>
       <c r="H41" s="3">
-        <v>12413500</v>
+        <v>12449000</v>
       </c>
       <c r="I41" s="3">
-        <v>5071300</v>
+        <v>5085800</v>
       </c>
       <c r="J41" s="3">
-        <v>9586000</v>
+        <v>9613400</v>
       </c>
       <c r="K41" s="3">
         <v>24153800</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9512200</v>
+        <v>9539400</v>
       </c>
       <c r="E42" s="3">
-        <v>8605100</v>
+        <v>8629700</v>
       </c>
       <c r="F42" s="3">
-        <v>9937500</v>
+        <v>9965900</v>
       </c>
       <c r="G42" s="3">
-        <v>10080700</v>
+        <v>10109500</v>
       </c>
       <c r="H42" s="3">
-        <v>16500700</v>
+        <v>16547800</v>
       </c>
       <c r="I42" s="3">
-        <v>9542600</v>
+        <v>9569800</v>
       </c>
       <c r="J42" s="3">
-        <v>6640200</v>
+        <v>6659200</v>
       </c>
       <c r="K42" s="3">
         <v>9425000</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10488700</v>
+        <v>10518700</v>
       </c>
       <c r="E43" s="3">
-        <v>10885800</v>
+        <v>10916900</v>
       </c>
       <c r="F43" s="3">
-        <v>10889100</v>
+        <v>10920200</v>
       </c>
       <c r="G43" s="3">
-        <v>11172200</v>
+        <v>11204200</v>
       </c>
       <c r="H43" s="3">
-        <v>11969700</v>
+        <v>12003900</v>
       </c>
       <c r="I43" s="3">
-        <v>9492700</v>
+        <v>9519800</v>
       </c>
       <c r="J43" s="3">
-        <v>8901300</v>
+        <v>8926800</v>
       </c>
       <c r="K43" s="3">
         <v>18023000</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1037300</v>
+        <v>1040200</v>
       </c>
       <c r="E44" s="3">
-        <v>907100</v>
+        <v>909700</v>
       </c>
       <c r="F44" s="3">
-        <v>733500</v>
+        <v>735600</v>
       </c>
       <c r="G44" s="3">
-        <v>648800</v>
+        <v>650700</v>
       </c>
       <c r="H44" s="3">
-        <v>774700</v>
+        <v>776900</v>
       </c>
       <c r="I44" s="3">
-        <v>630400</v>
+        <v>632200</v>
       </c>
       <c r="J44" s="3">
-        <v>625000</v>
+        <v>626700</v>
       </c>
       <c r="K44" s="3">
         <v>1542100</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1428900</v>
+        <v>1433000</v>
       </c>
       <c r="E45" s="3">
-        <v>1391000</v>
+        <v>1394900</v>
       </c>
       <c r="F45" s="3">
-        <v>1433300</v>
+        <v>1437400</v>
       </c>
       <c r="G45" s="3">
-        <v>1849900</v>
+        <v>1855200</v>
       </c>
       <c r="H45" s="3">
-        <v>1542900</v>
+        <v>1547300</v>
       </c>
       <c r="I45" s="3">
-        <v>1445200</v>
+        <v>1449300</v>
       </c>
       <c r="J45" s="3">
-        <v>1960600</v>
+        <v>1966200</v>
       </c>
       <c r="K45" s="3">
         <v>6462500</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>33268300</v>
+        <v>33363300</v>
       </c>
       <c r="E46" s="3">
-        <v>29922100</v>
+        <v>30007600</v>
       </c>
       <c r="F46" s="3">
-        <v>29309100</v>
+        <v>29392800</v>
       </c>
       <c r="G46" s="3">
-        <v>36071900</v>
+        <v>36175000</v>
       </c>
       <c r="H46" s="3">
-        <v>43201400</v>
+        <v>43324900</v>
       </c>
       <c r="I46" s="3">
-        <v>26182100</v>
+        <v>26256900</v>
       </c>
       <c r="J46" s="3">
-        <v>27713100</v>
+        <v>27792300</v>
       </c>
       <c r="K46" s="3">
         <v>34394000</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>21716300</v>
+        <v>15317200</v>
       </c>
       <c r="E47" s="3">
-        <v>13865200</v>
+        <v>9066000</v>
       </c>
       <c r="F47" s="3">
-        <v>11253600</v>
+        <v>7848500</v>
       </c>
       <c r="G47" s="3">
-        <v>18462400</v>
+        <v>9102000</v>
       </c>
       <c r="H47" s="3">
-        <v>10841300</v>
+        <v>10872300</v>
       </c>
       <c r="I47" s="3">
-        <v>10598300</v>
+        <v>10628600</v>
       </c>
       <c r="J47" s="3">
-        <v>12115100</v>
+        <v>12149700</v>
       </c>
       <c r="K47" s="3">
         <v>11741400</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>41221300</v>
+        <v>41339100</v>
       </c>
       <c r="E48" s="3">
-        <v>44272300</v>
+        <v>44398800</v>
       </c>
       <c r="F48" s="3">
-        <v>44748700</v>
+        <v>44876500</v>
       </c>
       <c r="G48" s="3">
-        <v>43522600</v>
+        <v>43647000</v>
       </c>
       <c r="H48" s="3">
-        <v>29763700</v>
+        <v>29848800</v>
       </c>
       <c r="I48" s="3">
-        <v>30732600</v>
+        <v>30820400</v>
       </c>
       <c r="J48" s="3">
-        <v>32771300</v>
+        <v>32865000</v>
       </c>
       <c r="K48" s="3">
         <v>76492200</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>51219600</v>
+        <v>51365900</v>
       </c>
       <c r="E49" s="3">
-        <v>57769700</v>
+        <v>57934800</v>
       </c>
       <c r="F49" s="3">
-        <v>58100700</v>
+        <v>58266700</v>
       </c>
       <c r="G49" s="3">
-        <v>58599800</v>
+        <v>58767200</v>
       </c>
       <c r="H49" s="3">
-        <v>44490400</v>
+        <v>44617500</v>
       </c>
       <c r="I49" s="3">
-        <v>46933800</v>
+        <v>47067900</v>
       </c>
       <c r="J49" s="3">
-        <v>50148700</v>
+        <v>50292000</v>
       </c>
       <c r="K49" s="3">
         <v>126135000</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>21314800</v>
+        <v>27836900</v>
       </c>
       <c r="E52" s="3">
-        <v>22354300</v>
+        <v>27256900</v>
       </c>
       <c r="F52" s="3">
-        <v>24831300</v>
+        <v>28339600</v>
       </c>
       <c r="G52" s="3">
-        <v>25805600</v>
+        <v>35292500</v>
       </c>
       <c r="H52" s="3">
-        <v>26708400</v>
+        <v>26784700</v>
       </c>
       <c r="I52" s="3">
-        <v>43541000</v>
+        <v>43665500</v>
       </c>
       <c r="J52" s="3">
-        <v>45083900</v>
+        <v>45212700</v>
       </c>
       <c r="K52" s="3">
         <v>34662200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>168740000</v>
+        <v>169222000</v>
       </c>
       <c r="E54" s="3">
-        <v>167143000</v>
+        <v>167621000</v>
       </c>
       <c r="F54" s="3">
-        <v>168243000</v>
+        <v>168724000</v>
       </c>
       <c r="G54" s="3">
-        <v>182462000</v>
+        <v>182984000</v>
       </c>
       <c r="H54" s="3">
-        <v>155005000</v>
+        <v>155448000</v>
       </c>
       <c r="I54" s="3">
-        <v>157988000</v>
+        <v>158439000</v>
       </c>
       <c r="J54" s="3">
-        <v>167832000</v>
+        <v>168312000</v>
       </c>
       <c r="K54" s="3">
         <v>182111000</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8670200</v>
+        <v>8695000</v>
       </c>
       <c r="E57" s="3">
-        <v>7993200</v>
+        <v>8016000</v>
       </c>
       <c r="F57" s="3">
-        <v>7350900</v>
+        <v>7371900</v>
       </c>
       <c r="G57" s="3">
-        <v>7320500</v>
+        <v>7341400</v>
       </c>
       <c r="H57" s="3">
-        <v>7125200</v>
+        <v>7145600</v>
       </c>
       <c r="I57" s="3">
-        <v>6740000</v>
+        <v>6759300</v>
       </c>
       <c r="J57" s="3">
-        <v>6755200</v>
+        <v>6774500</v>
       </c>
       <c r="K57" s="3">
         <v>8062800</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>15972300</v>
+        <v>16017900</v>
       </c>
       <c r="E58" s="3">
-        <v>12977700</v>
+        <v>13014800</v>
       </c>
       <c r="F58" s="3">
-        <v>9209500</v>
+        <v>9235800</v>
       </c>
       <c r="G58" s="3">
-        <v>12994000</v>
+        <v>13031100</v>
       </c>
       <c r="H58" s="3">
-        <v>4632900</v>
+        <v>4646200</v>
       </c>
       <c r="I58" s="3">
-        <v>11230800</v>
+        <v>11262900</v>
       </c>
       <c r="J58" s="3">
-        <v>13075300</v>
+        <v>13112700</v>
       </c>
       <c r="K58" s="3">
         <v>29470400</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12881100</v>
+        <v>12917900</v>
       </c>
       <c r="E59" s="3">
-        <v>15536100</v>
+        <v>15580500</v>
       </c>
       <c r="F59" s="3">
-        <v>14591100</v>
+        <v>14632800</v>
       </c>
       <c r="G59" s="3">
-        <v>15908300</v>
+        <v>15953700</v>
       </c>
       <c r="H59" s="3">
-        <v>15934300</v>
+        <v>15979800</v>
       </c>
       <c r="I59" s="3">
-        <v>24370200</v>
+        <v>24439800</v>
       </c>
       <c r="J59" s="3">
-        <v>26161500</v>
+        <v>26236300</v>
       </c>
       <c r="K59" s="3">
         <v>20263000</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37523600</v>
+        <v>37630900</v>
       </c>
       <c r="E60" s="3">
-        <v>36507000</v>
+        <v>36611300</v>
       </c>
       <c r="F60" s="3">
-        <v>31151400</v>
+        <v>31240400</v>
       </c>
       <c r="G60" s="3">
-        <v>36222700</v>
+        <v>36326200</v>
       </c>
       <c r="H60" s="3">
-        <v>27692500</v>
+        <v>27771600</v>
       </c>
       <c r="I60" s="3">
-        <v>42341000</v>
+        <v>42462000</v>
       </c>
       <c r="J60" s="3">
-        <v>45992100</v>
+        <v>46123500</v>
       </c>
       <c r="K60" s="3">
         <v>45482900</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>56060900</v>
+        <v>56221000</v>
       </c>
       <c r="E61" s="3">
-        <v>63072100</v>
+        <v>63252300</v>
       </c>
       <c r="F61" s="3">
-        <v>64310100</v>
+        <v>64493900</v>
       </c>
       <c r="G61" s="3">
-        <v>68299700</v>
+        <v>68494800</v>
       </c>
       <c r="H61" s="3">
-        <v>52823200</v>
+        <v>52974100</v>
       </c>
       <c r="I61" s="3">
-        <v>35403500</v>
+        <v>35504700</v>
       </c>
       <c r="J61" s="3">
-        <v>37126500</v>
+        <v>37232600</v>
       </c>
       <c r="K61" s="3">
         <v>39621300</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5191700</v>
+        <v>5206600</v>
       </c>
       <c r="E62" s="3">
-        <v>5639800</v>
+        <v>5655900</v>
       </c>
       <c r="F62" s="3">
-        <v>10051400</v>
+        <v>10080200</v>
       </c>
       <c r="G62" s="3">
-        <v>9991800</v>
+        <v>10020300</v>
       </c>
       <c r="H62" s="3">
-        <v>5651800</v>
+        <v>5667900</v>
       </c>
       <c r="I62" s="3">
-        <v>5804800</v>
+        <v>5821300</v>
       </c>
       <c r="J62" s="3">
-        <v>4728400</v>
+        <v>4741900</v>
       </c>
       <c r="K62" s="3">
         <v>7369200</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>99952400</v>
+        <v>100238000</v>
       </c>
       <c r="E66" s="3">
-        <v>107704000</v>
+        <v>108011000</v>
       </c>
       <c r="F66" s="3">
-        <v>107696000</v>
+        <v>108004000</v>
       </c>
       <c r="G66" s="3">
-        <v>115832000</v>
+        <v>116163000</v>
       </c>
       <c r="H66" s="3">
-        <v>87498700</v>
+        <v>87748700</v>
       </c>
       <c r="I66" s="3">
-        <v>84598500</v>
+        <v>84840200</v>
       </c>
       <c r="J66" s="3">
-        <v>89495100</v>
+        <v>89750800</v>
       </c>
       <c r="K66" s="3">
         <v>92378600</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>68787900</v>
+        <v>68984500</v>
       </c>
       <c r="E76" s="3">
-        <v>59439600</v>
+        <v>59609400</v>
       </c>
       <c r="F76" s="3">
-        <v>60547300</v>
+        <v>60720300</v>
       </c>
       <c r="G76" s="3">
-        <v>66629800</v>
+        <v>66820200</v>
       </c>
       <c r="H76" s="3">
-        <v>67506500</v>
+        <v>67699400</v>
       </c>
       <c r="I76" s="3">
-        <v>73389400</v>
+        <v>73599100</v>
       </c>
       <c r="J76" s="3">
-        <v>78337000</v>
+        <v>78560800</v>
       </c>
       <c r="K76" s="3">
         <v>89732700</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12844200</v>
+        <v>12880900</v>
       </c>
       <c r="E81" s="3">
-        <v>2427100</v>
+        <v>2434100</v>
       </c>
       <c r="F81" s="3">
-        <v>64000</v>
+        <v>64200</v>
       </c>
       <c r="G81" s="3">
-        <v>-998200</v>
+        <v>-1001100</v>
       </c>
       <c r="H81" s="3">
-        <v>-8701700</v>
+        <v>-8726600</v>
       </c>
       <c r="I81" s="3">
-        <v>2646300</v>
+        <v>2653900</v>
       </c>
       <c r="J81" s="3">
-        <v>-6832200</v>
+        <v>-6851800</v>
       </c>
       <c r="K81" s="3">
         <v>-5820600</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>14775500</v>
+        <v>14817700</v>
       </c>
       <c r="E83" s="3">
-        <v>15021800</v>
+        <v>15064700</v>
       </c>
       <c r="F83" s="3">
-        <v>15299600</v>
+        <v>15343300</v>
       </c>
       <c r="G83" s="3">
-        <v>15378800</v>
+        <v>15422700</v>
       </c>
       <c r="H83" s="3">
-        <v>10627600</v>
+        <v>10657900</v>
       </c>
       <c r="I83" s="3">
-        <v>11293800</v>
+        <v>11326000</v>
       </c>
       <c r="J83" s="3">
-        <v>12028300</v>
+        <v>12062700</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>8</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>19588600</v>
+        <v>19644600</v>
       </c>
       <c r="E89" s="3">
-        <v>19617900</v>
+        <v>19673900</v>
       </c>
       <c r="F89" s="3">
-        <v>18678300</v>
+        <v>18731600</v>
       </c>
       <c r="G89" s="3">
-        <v>18856200</v>
+        <v>18910100</v>
       </c>
       <c r="H89" s="3">
-        <v>14083300</v>
+        <v>14123500</v>
       </c>
       <c r="I89" s="3">
-        <v>14756000</v>
+        <v>14798200</v>
       </c>
       <c r="J89" s="3">
-        <v>15432000</v>
+        <v>15476000</v>
       </c>
       <c r="K89" s="3">
         <v>13642200</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6781300</v>
+        <v>-6800600</v>
       </c>
       <c r="E91" s="3">
-        <v>-6290800</v>
+        <v>-6308800</v>
       </c>
       <c r="F91" s="3">
-        <v>-5873100</v>
+        <v>-5889900</v>
       </c>
       <c r="G91" s="3">
-        <v>-5622500</v>
+        <v>-5638500</v>
       </c>
       <c r="H91" s="3">
-        <v>-5482500</v>
+        <v>-5498200</v>
       </c>
       <c r="I91" s="3">
-        <v>-5334900</v>
+        <v>-5350200</v>
       </c>
       <c r="J91" s="3">
-        <v>-6819200</v>
+        <v>-6838700</v>
       </c>
       <c r="K91" s="3">
         <v>-7887200</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-411200</v>
+        <v>-412400</v>
       </c>
       <c r="E94" s="3">
-        <v>-7451800</v>
+        <v>-7473100</v>
       </c>
       <c r="F94" s="3">
-        <v>-10049300</v>
+        <v>-10078000</v>
       </c>
       <c r="G94" s="3">
-        <v>-8775500</v>
+        <v>-8800600</v>
       </c>
       <c r="H94" s="3">
-        <v>-10000400</v>
+        <v>-10029000</v>
       </c>
       <c r="I94" s="3">
-        <v>-10677500</v>
+        <v>-10708000</v>
       </c>
       <c r="J94" s="3">
-        <v>-9139000</v>
+        <v>-9165100</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2695100</v>
+        <v>-2702800</v>
       </c>
       <c r="E96" s="3">
-        <v>-2684300</v>
+        <v>-2692000</v>
       </c>
       <c r="F96" s="3">
-        <v>-2633300</v>
+        <v>-2640800</v>
       </c>
       <c r="G96" s="3">
-        <v>-2491200</v>
+        <v>-2498300</v>
       </c>
       <c r="H96" s="3">
-        <v>-4409400</v>
+        <v>-4422000</v>
       </c>
       <c r="I96" s="3">
-        <v>-4253200</v>
+        <v>-4265400</v>
       </c>
       <c r="J96" s="3">
-        <v>-4029700</v>
+        <v>-4041200</v>
       </c>
       <c r="K96" s="3">
         <v>-4047000</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-14571600</v>
+        <v>-14613200</v>
       </c>
       <c r="E100" s="3">
-        <v>-10531000</v>
+        <v>-10561100</v>
       </c>
       <c r="F100" s="3">
-        <v>-16487700</v>
+        <v>-16534800</v>
       </c>
       <c r="G100" s="3">
-        <v>-10146900</v>
+        <v>-10175900</v>
       </c>
       <c r="H100" s="3">
-        <v>4814100</v>
+        <v>4827900</v>
       </c>
       <c r="I100" s="3">
-        <v>-7848900</v>
+        <v>-7871300</v>
       </c>
       <c r="J100" s="3">
-        <v>-9869200</v>
+        <v>-9897400</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>13000</v>
+        <v>13100</v>
       </c>
       <c r="E101" s="3">
-        <v>80300</v>
+        <v>80500</v>
       </c>
       <c r="F101" s="3">
-        <v>-276700</v>
+        <v>-277500</v>
       </c>
       <c r="G101" s="3">
-        <v>-277800</v>
+        <v>-278600</v>
       </c>
       <c r="H101" s="3">
-        <v>11900</v>
+        <v>12000</v>
       </c>
       <c r="I101" s="3">
-        <v>-469800</v>
+        <v>-471100</v>
       </c>
       <c r="J101" s="3">
-        <v>-339600</v>
+        <v>-340600</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>8</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>4618800</v>
+        <v>4632000</v>
       </c>
       <c r="E102" s="3">
-        <v>1715400</v>
+        <v>1720300</v>
       </c>
       <c r="F102" s="3">
-        <v>-8135300</v>
+        <v>-8158600</v>
       </c>
       <c r="G102" s="3">
-        <v>-343900</v>
+        <v>-344900</v>
       </c>
       <c r="H102" s="3">
-        <v>8908900</v>
+        <v>8934400</v>
       </c>
       <c r="I102" s="3">
-        <v>-4240200</v>
+        <v>-4252300</v>
       </c>
       <c r="J102" s="3">
-        <v>-3915800</v>
+        <v>-3927000</v>
       </c>
       <c r="K102" s="3">
         <v>-2964700</v>

--- a/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>49732700</v>
+        <v>39680100</v>
       </c>
       <c r="E8" s="3">
-        <v>49595600</v>
+        <v>40712100</v>
       </c>
       <c r="F8" s="3">
-        <v>47668600</v>
+        <v>39996700</v>
       </c>
       <c r="G8" s="3">
-        <v>48936200</v>
+        <v>47344400</v>
       </c>
       <c r="H8" s="3">
-        <v>47513000</v>
+        <v>48603400</v>
       </c>
       <c r="I8" s="3">
-        <v>50673900</v>
+        <v>47189800</v>
       </c>
       <c r="J8" s="3">
+        <v>50329300</v>
+      </c>
+      <c r="K8" s="3">
         <v>51827300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>53640400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>50218800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>46973500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>42134200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>43556800</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>33567900</v>
+        <v>26432800</v>
       </c>
       <c r="E9" s="3">
-        <v>33267600</v>
+        <v>26324800</v>
       </c>
       <c r="F9" s="3">
-        <v>32736600</v>
+        <v>25880600</v>
       </c>
       <c r="G9" s="3">
-        <v>33385100</v>
+        <v>32513900</v>
       </c>
       <c r="H9" s="3">
-        <v>32817100</v>
+        <v>33158000</v>
       </c>
       <c r="I9" s="3">
-        <v>35658100</v>
+        <v>32593900</v>
       </c>
       <c r="J9" s="3">
+        <v>35415600</v>
+      </c>
+      <c r="K9" s="3">
         <v>37622100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39536200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36402300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>34228700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>29425600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>30519200</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>16164800</v>
+        <v>13247200</v>
       </c>
       <c r="E10" s="3">
-        <v>16328000</v>
+        <v>14387400</v>
       </c>
       <c r="F10" s="3">
-        <v>14932000</v>
+        <v>14116100</v>
       </c>
       <c r="G10" s="3">
-        <v>15551100</v>
+        <v>14830400</v>
       </c>
       <c r="H10" s="3">
-        <v>14695900</v>
+        <v>15445400</v>
       </c>
       <c r="I10" s="3">
-        <v>15015800</v>
+        <v>14595900</v>
       </c>
       <c r="J10" s="3">
+        <v>14913700</v>
+      </c>
+      <c r="K10" s="3">
         <v>14205100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14104200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13816500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12744800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12708600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13037500</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-9970300</v>
+        <v>-69200</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-10034300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>87500</v>
       </c>
       <c r="G14" s="3">
-        <v>1833400</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>3835600</v>
+        <v>1821000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>3809500</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1387300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>612800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>8084900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>8528500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4544100</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>34177200</v>
+        <v>35719300</v>
       </c>
       <c r="E17" s="3">
-        <v>43270500</v>
+        <v>25094900</v>
       </c>
       <c r="F17" s="3">
-        <v>42087700</v>
+        <v>33793500</v>
       </c>
       <c r="G17" s="3">
-        <v>44476100</v>
+        <v>41801500</v>
       </c>
       <c r="H17" s="3">
-        <v>48547800</v>
+        <v>44173600</v>
       </c>
       <c r="I17" s="3">
-        <v>45996200</v>
+        <v>48217600</v>
       </c>
       <c r="J17" s="3">
+        <v>45683400</v>
+      </c>
+      <c r="K17" s="3">
         <v>47774100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>52218900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>48067200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51766900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>44573100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37253400</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15555500</v>
+        <v>3960800</v>
       </c>
       <c r="E18" s="3">
-        <v>6325100</v>
+        <v>15617200</v>
       </c>
       <c r="F18" s="3">
-        <v>5580900</v>
+        <v>6203200</v>
       </c>
       <c r="G18" s="3">
-        <v>4460100</v>
+        <v>5542900</v>
       </c>
       <c r="H18" s="3">
-        <v>-1034800</v>
+        <v>4429800</v>
       </c>
       <c r="I18" s="3">
-        <v>4677700</v>
+        <v>-1027700</v>
       </c>
       <c r="J18" s="3">
+        <v>4645900</v>
+      </c>
+      <c r="K18" s="3">
         <v>4053200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1421500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2151600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4793400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2438900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6303300</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1193600</v>
+        <v>759700</v>
       </c>
       <c r="E20" s="3">
-        <v>764900</v>
+        <v>1168200</v>
       </c>
       <c r="F20" s="3">
-        <v>1933600</v>
+        <v>756500</v>
       </c>
       <c r="G20" s="3">
-        <v>-585400</v>
+        <v>1920400</v>
       </c>
       <c r="H20" s="3">
-        <v>-51100</v>
+        <v>-581400</v>
       </c>
       <c r="I20" s="3">
-        <v>733400</v>
+        <v>-50800</v>
       </c>
       <c r="J20" s="3">
+        <v>728400</v>
+      </c>
+      <c r="K20" s="3">
         <v>280700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-596600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1216400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-283000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2137700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2065600</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>31655200</v>
+        <v>15904000</v>
       </c>
       <c r="E21" s="3">
-        <v>22244700</v>
+        <v>31409700</v>
       </c>
       <c r="F21" s="3">
-        <v>22949200</v>
+        <v>21827700</v>
       </c>
       <c r="G21" s="3">
-        <v>19389400</v>
+        <v>22606200</v>
       </c>
       <c r="H21" s="3">
-        <v>9635600</v>
+        <v>19069700</v>
       </c>
       <c r="I21" s="3">
-        <v>16804700</v>
+        <v>9440200</v>
       </c>
       <c r="J21" s="3">
+        <v>16552400</v>
+      </c>
+      <c r="K21" s="3">
         <v>16468500</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>15043600</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>15928000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2804000</v>
+        <v>2969800</v>
       </c>
       <c r="E22" s="3">
-        <v>2625600</v>
+        <v>2656400</v>
       </c>
       <c r="F22" s="3">
-        <v>2784400</v>
+        <v>2475900</v>
       </c>
       <c r="G22" s="3">
-        <v>3009700</v>
+        <v>2765500</v>
       </c>
       <c r="H22" s="3">
-        <v>1757300</v>
+        <v>2989200</v>
       </c>
       <c r="I22" s="3">
-        <v>1191500</v>
+        <v>1745300</v>
       </c>
       <c r="J22" s="3">
+        <v>1183400</v>
+      </c>
+      <c r="K22" s="3">
         <v>1295900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1029500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1568300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1379300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3556500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3719400</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>13945100</v>
+        <v>1750700</v>
       </c>
       <c r="E23" s="3">
-        <v>4464500</v>
+        <v>14129100</v>
       </c>
       <c r="F23" s="3">
-        <v>4730000</v>
+        <v>4483800</v>
       </c>
       <c r="G23" s="3">
-        <v>865000</v>
+        <v>4697800</v>
       </c>
       <c r="H23" s="3">
-        <v>-2843200</v>
+        <v>859200</v>
       </c>
       <c r="I23" s="3">
-        <v>4219700</v>
+        <v>-2823900</v>
       </c>
       <c r="J23" s="3">
+        <v>4191000</v>
+      </c>
+      <c r="K23" s="3">
         <v>3038000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-204600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1799700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-6455700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3857800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4649500</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>523400</v>
+        <v>54000</v>
       </c>
       <c r="E24" s="3">
-        <v>1447200</v>
+        <v>531700</v>
       </c>
       <c r="F24" s="3">
-        <v>4204400</v>
+        <v>1687000</v>
       </c>
       <c r="G24" s="3">
-        <v>1360100</v>
+        <v>4175800</v>
       </c>
       <c r="H24" s="3">
-        <v>1627800</v>
+        <v>1350900</v>
       </c>
       <c r="I24" s="3">
-        <v>-956400</v>
+        <v>1616700</v>
       </c>
       <c r="J24" s="3">
+        <v>-949900</v>
+      </c>
+      <c r="K24" s="3">
         <v>5183700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5316700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-6301100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-20312800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>527200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>791000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>13421700</v>
+        <v>1696700</v>
       </c>
       <c r="E26" s="3">
-        <v>3017300</v>
+        <v>13597400</v>
       </c>
       <c r="F26" s="3">
-        <v>525600</v>
+        <v>2796900</v>
       </c>
       <c r="G26" s="3">
-        <v>-495100</v>
+        <v>522000</v>
       </c>
       <c r="H26" s="3">
-        <v>-4471000</v>
+        <v>-491700</v>
       </c>
       <c r="I26" s="3">
-        <v>5176100</v>
+        <v>-4440600</v>
       </c>
       <c r="J26" s="3">
+        <v>5140900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-2145700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5521300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8100800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13857100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4385000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3858500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>12880900</v>
+        <v>1302200</v>
       </c>
       <c r="E27" s="3">
-        <v>2434100</v>
+        <v>13060300</v>
       </c>
       <c r="F27" s="3">
-        <v>64200</v>
+        <v>2217600</v>
       </c>
       <c r="G27" s="3">
-        <v>-1001100</v>
+        <v>63800</v>
       </c>
       <c r="H27" s="3">
-        <v>-4880100</v>
+        <v>-994200</v>
       </c>
       <c r="I27" s="3">
-        <v>4796300</v>
+        <v>-4846900</v>
       </c>
       <c r="J27" s="3">
+        <v>4763700</v>
+      </c>
+      <c r="K27" s="3">
         <v>-2382900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5826000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7895300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13653700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4655200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3806900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,51 +1580,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-266900</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>199900</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>-3846400</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-2142500</v>
+        <v>-3820300</v>
       </c>
       <c r="J29" s="3">
+        <v>-2127900</v>
+      </c>
+      <c r="K29" s="3">
         <v>-4468800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>5400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-281300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>58931800</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>5112700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>3988700</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1193600</v>
+        <v>-759700</v>
       </c>
       <c r="E32" s="3">
-        <v>-764900</v>
+        <v>-1168200</v>
       </c>
       <c r="F32" s="3">
-        <v>-1933600</v>
+        <v>-756500</v>
       </c>
       <c r="G32" s="3">
-        <v>585400</v>
+        <v>-1920400</v>
       </c>
       <c r="H32" s="3">
-        <v>51100</v>
+        <v>581400</v>
       </c>
       <c r="I32" s="3">
-        <v>-733400</v>
+        <v>50800</v>
       </c>
       <c r="J32" s="3">
+        <v>-728400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-280700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>596600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1216400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>283000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2137700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2065600</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>12880900</v>
+        <v>1232000</v>
       </c>
       <c r="E33" s="3">
-        <v>2434100</v>
+        <v>12793300</v>
       </c>
       <c r="F33" s="3">
-        <v>64200</v>
+        <v>2417500</v>
       </c>
       <c r="G33" s="3">
-        <v>-1001100</v>
+        <v>63800</v>
       </c>
       <c r="H33" s="3">
-        <v>-8726600</v>
+        <v>-994200</v>
       </c>
       <c r="I33" s="3">
-        <v>2653900</v>
+        <v>-8667200</v>
       </c>
       <c r="J33" s="3">
+        <v>2635800</v>
+      </c>
+      <c r="K33" s="3">
         <v>-6851800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5820600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7614000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>72585600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>457400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7795600</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>12880900</v>
+        <v>1232000</v>
       </c>
       <c r="E35" s="3">
-        <v>2434100</v>
+        <v>12793300</v>
       </c>
       <c r="F35" s="3">
-        <v>64200</v>
+        <v>2417500</v>
       </c>
       <c r="G35" s="3">
-        <v>-1001100</v>
+        <v>63800</v>
       </c>
       <c r="H35" s="3">
-        <v>-8726600</v>
+        <v>-994200</v>
       </c>
       <c r="I35" s="3">
-        <v>2653900</v>
+        <v>-8667200</v>
       </c>
       <c r="J35" s="3">
+        <v>2635800</v>
+      </c>
+      <c r="K35" s="3">
         <v>-6851800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5820600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7614000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>72585600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>457400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7795600</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>10832000</v>
+        <v>4483800</v>
       </c>
       <c r="E41" s="3">
-        <v>10572000</v>
+        <v>10758400</v>
       </c>
       <c r="F41" s="3">
-        <v>6333800</v>
+        <v>10500100</v>
       </c>
       <c r="G41" s="3">
-        <v>12355400</v>
+        <v>6290800</v>
       </c>
       <c r="H41" s="3">
-        <v>12449000</v>
+        <v>12271300</v>
       </c>
       <c r="I41" s="3">
-        <v>5085800</v>
+        <v>12364300</v>
       </c>
       <c r="J41" s="3">
+        <v>5051200</v>
+      </c>
+      <c r="K41" s="3">
         <v>9613400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24153800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14844000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>18717800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8357900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8008800</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>9539400</v>
+        <v>7701100</v>
       </c>
       <c r="E42" s="3">
-        <v>8629700</v>
+        <v>9474500</v>
       </c>
       <c r="F42" s="3">
-        <v>9965900</v>
+        <v>8571000</v>
       </c>
       <c r="G42" s="3">
-        <v>10109500</v>
+        <v>9898100</v>
       </c>
       <c r="H42" s="3">
-        <v>16547800</v>
+        <v>10040800</v>
       </c>
       <c r="I42" s="3">
-        <v>9569800</v>
+        <v>16435300</v>
       </c>
       <c r="J42" s="3">
+        <v>9504800</v>
+      </c>
+      <c r="K42" s="3">
         <v>6659200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9425000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7715700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11523500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8970500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1484400</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10518700</v>
+        <v>8488900</v>
       </c>
       <c r="E43" s="3">
-        <v>10916900</v>
+        <v>10447100</v>
       </c>
       <c r="F43" s="3">
-        <v>10920200</v>
+        <v>10842700</v>
       </c>
       <c r="G43" s="3">
-        <v>11204200</v>
+        <v>10845900</v>
       </c>
       <c r="H43" s="3">
-        <v>12003900</v>
+        <v>11128000</v>
       </c>
       <c r="I43" s="3">
-        <v>9519800</v>
+        <v>11922300</v>
       </c>
       <c r="J43" s="3">
+        <v>9455000</v>
+      </c>
+      <c r="K43" s="3">
         <v>8926800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>18023000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>17585100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>11390000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5397000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8098500</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1040200</v>
+        <v>613800</v>
       </c>
       <c r="E44" s="3">
-        <v>909700</v>
+        <v>1033100</v>
       </c>
       <c r="F44" s="3">
-        <v>735600</v>
+        <v>903500</v>
       </c>
       <c r="G44" s="3">
-        <v>650700</v>
+        <v>730600</v>
       </c>
       <c r="H44" s="3">
-        <v>776900</v>
+        <v>646300</v>
       </c>
       <c r="I44" s="3">
-        <v>632200</v>
+        <v>771600</v>
       </c>
       <c r="J44" s="3">
+        <v>627900</v>
+      </c>
+      <c r="K44" s="3">
         <v>626700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1542100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1192500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1080400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>891200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>545300</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1433000</v>
+        <v>880800</v>
       </c>
       <c r="E45" s="3">
-        <v>1394900</v>
+        <v>1423300</v>
       </c>
       <c r="F45" s="3">
-        <v>1437400</v>
+        <v>1385500</v>
       </c>
       <c r="G45" s="3">
-        <v>1855200</v>
+        <v>1427600</v>
       </c>
       <c r="H45" s="3">
-        <v>1547300</v>
+        <v>1842600</v>
       </c>
       <c r="I45" s="3">
-        <v>1449300</v>
+        <v>1536800</v>
       </c>
       <c r="J45" s="3">
+        <v>1439500</v>
+      </c>
+      <c r="K45" s="3">
         <v>1966200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6462500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3161400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>526700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3942000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4330900</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>33363300</v>
+        <v>22168400</v>
       </c>
       <c r="E46" s="3">
-        <v>30007600</v>
+        <v>33136400</v>
       </c>
       <c r="F46" s="3">
-        <v>29392800</v>
+        <v>29803500</v>
       </c>
       <c r="G46" s="3">
-        <v>36175000</v>
+        <v>29192900</v>
       </c>
       <c r="H46" s="3">
-        <v>43324900</v>
+        <v>35929000</v>
       </c>
       <c r="I46" s="3">
-        <v>26256900</v>
+        <v>43030200</v>
       </c>
       <c r="J46" s="3">
+        <v>26078400</v>
+      </c>
+      <c r="K46" s="3">
         <v>27792300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>34394000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>28497600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>30284200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>24026100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>22467800</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>15317200</v>
+        <v>13784300</v>
       </c>
       <c r="E47" s="3">
-        <v>9066000</v>
+        <v>15213000</v>
       </c>
       <c r="F47" s="3">
-        <v>7848500</v>
+        <v>9004400</v>
       </c>
       <c r="G47" s="3">
-        <v>9102000</v>
+        <v>7795100</v>
       </c>
       <c r="H47" s="3">
-        <v>10872300</v>
+        <v>9040100</v>
       </c>
       <c r="I47" s="3">
-        <v>10628600</v>
+        <v>10798400</v>
       </c>
       <c r="J47" s="3">
+        <v>10556300</v>
+      </c>
+      <c r="K47" s="3">
         <v>12149700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11741400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>13054700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8497800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>62541700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>44185100</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>41339100</v>
+        <v>30798900</v>
       </c>
       <c r="E48" s="3">
-        <v>44398800</v>
+        <v>41058000</v>
       </c>
       <c r="F48" s="3">
-        <v>44876500</v>
+        <v>44096900</v>
       </c>
       <c r="G48" s="3">
-        <v>43647000</v>
+        <v>44571300</v>
       </c>
       <c r="H48" s="3">
-        <v>29848800</v>
+        <v>43350100</v>
       </c>
       <c r="I48" s="3">
-        <v>30820400</v>
+        <v>29645800</v>
       </c>
       <c r="J48" s="3">
+        <v>30610800</v>
+      </c>
+      <c r="K48" s="3">
         <v>32865000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>76492200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>65812200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>55984500</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20930700</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>51365900</v>
+        <v>41987400</v>
       </c>
       <c r="E49" s="3">
-        <v>57934800</v>
+        <v>51016600</v>
       </c>
       <c r="F49" s="3">
-        <v>58266700</v>
+        <v>57540800</v>
       </c>
       <c r="G49" s="3">
-        <v>58767200</v>
+        <v>57870400</v>
       </c>
       <c r="H49" s="3">
-        <v>44617500</v>
+        <v>58367500</v>
       </c>
       <c r="I49" s="3">
-        <v>47067900</v>
+        <v>44314100</v>
       </c>
       <c r="J49" s="3">
+        <v>46747800</v>
+      </c>
+      <c r="K49" s="3">
         <v>50292000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>126135000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>106907000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>114385000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>107136000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>66774100</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27836900</v>
+        <v>47260100</v>
       </c>
       <c r="E52" s="3">
-        <v>27256900</v>
+        <v>27647500</v>
       </c>
       <c r="F52" s="3">
-        <v>28339600</v>
+        <v>27071500</v>
       </c>
       <c r="G52" s="3">
-        <v>35292500</v>
+        <v>28146800</v>
       </c>
       <c r="H52" s="3">
-        <v>26784700</v>
+        <v>35052500</v>
       </c>
       <c r="I52" s="3">
-        <v>43665500</v>
+        <v>26602500</v>
       </c>
       <c r="J52" s="3">
+        <v>43368500</v>
+      </c>
+      <c r="K52" s="3">
         <v>45212700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>34662200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>34484200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25286200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3218400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2245100</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>169222000</v>
+        <v>155999000</v>
       </c>
       <c r="E54" s="3">
-        <v>167621000</v>
+        <v>168072000</v>
       </c>
       <c r="F54" s="3">
-        <v>168724000</v>
+        <v>166481000</v>
       </c>
       <c r="G54" s="3">
-        <v>182984000</v>
+        <v>167577000</v>
       </c>
       <c r="H54" s="3">
-        <v>155448000</v>
+        <v>181739000</v>
       </c>
       <c r="I54" s="3">
-        <v>158439000</v>
+        <v>154391000</v>
       </c>
       <c r="J54" s="3">
+        <v>157362000</v>
+      </c>
+      <c r="K54" s="3">
         <v>168312000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>182111000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>176006000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>149253000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>153512000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>156603000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8695000</v>
+        <v>6491800</v>
       </c>
       <c r="E57" s="3">
-        <v>8016000</v>
+        <v>8635900</v>
       </c>
       <c r="F57" s="3">
-        <v>7371900</v>
+        <v>7961500</v>
       </c>
       <c r="G57" s="3">
-        <v>7341400</v>
+        <v>7321700</v>
       </c>
       <c r="H57" s="3">
-        <v>7145600</v>
+        <v>7291500</v>
       </c>
       <c r="I57" s="3">
-        <v>6759300</v>
+        <v>7097000</v>
       </c>
       <c r="J57" s="3">
+        <v>6713300</v>
+      </c>
+      <c r="K57" s="3">
         <v>6774500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8062800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>26700000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5832200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>9059300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5098300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>16017900</v>
+        <v>9357800</v>
       </c>
       <c r="E58" s="3">
-        <v>13014800</v>
+        <v>15909000</v>
       </c>
       <c r="F58" s="3">
-        <v>9235800</v>
+        <v>12926300</v>
       </c>
       <c r="G58" s="3">
-        <v>13031100</v>
+        <v>9173000</v>
       </c>
       <c r="H58" s="3">
-        <v>4646200</v>
+        <v>12942500</v>
       </c>
       <c r="I58" s="3">
-        <v>11262900</v>
+        <v>4614600</v>
       </c>
       <c r="J58" s="3">
+        <v>11186300</v>
+      </c>
+      <c r="K58" s="3">
         <v>13112700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>29470400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27216900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5211100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14101100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5886000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>12917900</v>
+        <v>9312400</v>
       </c>
       <c r="E59" s="3">
-        <v>15580500</v>
+        <v>12830100</v>
       </c>
       <c r="F59" s="3">
-        <v>14632800</v>
+        <v>15474500</v>
       </c>
       <c r="G59" s="3">
-        <v>15953700</v>
+        <v>14533300</v>
       </c>
       <c r="H59" s="3">
-        <v>15979800</v>
+        <v>15845200</v>
       </c>
       <c r="I59" s="3">
-        <v>24439800</v>
+        <v>15871200</v>
       </c>
       <c r="J59" s="3">
+        <v>24273600</v>
+      </c>
+      <c r="K59" s="3">
         <v>26236300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20263000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16151800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24224200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17625800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15971500</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37630900</v>
+        <v>25161900</v>
       </c>
       <c r="E60" s="3">
-        <v>36611300</v>
+        <v>37374900</v>
       </c>
       <c r="F60" s="3">
-        <v>31240400</v>
+        <v>36362300</v>
       </c>
       <c r="G60" s="3">
-        <v>36326200</v>
+        <v>31028000</v>
       </c>
       <c r="H60" s="3">
-        <v>27771600</v>
+        <v>36079200</v>
       </c>
       <c r="I60" s="3">
-        <v>42462000</v>
+        <v>27582700</v>
       </c>
       <c r="J60" s="3">
+        <v>42173200</v>
+      </c>
+      <c r="K60" s="3">
         <v>46123500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>45482900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41494200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30672500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>31483900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26955800</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>56221000</v>
+        <v>52228100</v>
       </c>
       <c r="E61" s="3">
-        <v>63252300</v>
+        <v>55838700</v>
       </c>
       <c r="F61" s="3">
-        <v>64493900</v>
+        <v>62822200</v>
       </c>
       <c r="G61" s="3">
-        <v>68494800</v>
+        <v>64055300</v>
       </c>
       <c r="H61" s="3">
-        <v>52974100</v>
+        <v>68029000</v>
       </c>
       <c r="I61" s="3">
-        <v>35504700</v>
+        <v>52613900</v>
       </c>
       <c r="J61" s="3">
+        <v>35263200</v>
+      </c>
+      <c r="K61" s="3">
         <v>37232600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>39621300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>32215400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>26146200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>30132200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>31821900</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5206600</v>
+        <v>5212200</v>
       </c>
       <c r="E62" s="3">
-        <v>5655900</v>
+        <v>5171100</v>
       </c>
       <c r="F62" s="3">
-        <v>10080200</v>
+        <v>5617500</v>
       </c>
       <c r="G62" s="3">
-        <v>10020300</v>
+        <v>10011600</v>
       </c>
       <c r="H62" s="3">
-        <v>5667900</v>
+        <v>9952200</v>
       </c>
       <c r="I62" s="3">
-        <v>5821300</v>
+        <v>5629400</v>
       </c>
       <c r="J62" s="3">
+        <v>5781700</v>
+      </c>
+      <c r="K62" s="3">
         <v>4741900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7369200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6486900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6150700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13106700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10083300</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>100238000</v>
+        <v>91193800</v>
       </c>
       <c r="E66" s="3">
-        <v>108011000</v>
+        <v>99556200</v>
       </c>
       <c r="F66" s="3">
-        <v>108004000</v>
+        <v>107277000</v>
       </c>
       <c r="G66" s="3">
-        <v>116163000</v>
+        <v>107269000</v>
       </c>
       <c r="H66" s="3">
-        <v>87748700</v>
+        <v>115373000</v>
       </c>
       <c r="I66" s="3">
-        <v>84840200</v>
+        <v>87152000</v>
       </c>
       <c r="J66" s="3">
+        <v>84263300</v>
+      </c>
+      <c r="K66" s="3">
         <v>89750800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>92378600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>81027800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62521000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>74186800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>70282600</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,9 +3300,12 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3160,21 +3333,24 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>-89136900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-62998800</v>
       </c>
-      <c r="N72" s="3" t="s">
+      <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-94206800</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>68984500</v>
+        <v>64805300</v>
       </c>
       <c r="E76" s="3">
-        <v>59609400</v>
+        <v>68515300</v>
       </c>
       <c r="F76" s="3">
-        <v>60720300</v>
+        <v>59204000</v>
       </c>
       <c r="G76" s="3">
-        <v>66820200</v>
+        <v>60307400</v>
       </c>
       <c r="H76" s="3">
-        <v>67699400</v>
+        <v>66365800</v>
       </c>
       <c r="I76" s="3">
-        <v>73599100</v>
+        <v>67239000</v>
       </c>
       <c r="J76" s="3">
+        <v>73098500</v>
+      </c>
+      <c r="K76" s="3">
         <v>78560800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>89732700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>94978200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>86731700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>79325200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>86320300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>12880900</v>
+        <v>1232000</v>
       </c>
       <c r="E81" s="3">
-        <v>2434100</v>
+        <v>12793300</v>
       </c>
       <c r="F81" s="3">
-        <v>64200</v>
+        <v>2417500</v>
       </c>
       <c r="G81" s="3">
-        <v>-1001100</v>
+        <v>63800</v>
       </c>
       <c r="H81" s="3">
-        <v>-8726600</v>
+        <v>-994200</v>
       </c>
       <c r="I81" s="3">
-        <v>2653900</v>
+        <v>-8667200</v>
       </c>
       <c r="J81" s="3">
+        <v>2635800</v>
+      </c>
+      <c r="K81" s="3">
         <v>-6851800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5820600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7614000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>72585600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>457400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7795600</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>14817700</v>
+        <v>11254400</v>
       </c>
       <c r="E83" s="3">
-        <v>15064700</v>
+        <v>14717000</v>
       </c>
       <c r="F83" s="3">
-        <v>15343300</v>
+        <v>14962300</v>
       </c>
       <c r="G83" s="3">
-        <v>15422700</v>
+        <v>15239000</v>
       </c>
       <c r="H83" s="3">
-        <v>10657900</v>
+        <v>15317800</v>
       </c>
       <c r="I83" s="3">
-        <v>11326000</v>
+        <v>10585500</v>
       </c>
       <c r="J83" s="3">
+        <v>11249000</v>
+      </c>
+      <c r="K83" s="3">
         <v>12062700</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>11529000</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P83" s="3">
         <v>7540900</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>19644600</v>
+        <v>17893100</v>
       </c>
       <c r="E89" s="3">
-        <v>19673900</v>
+        <v>19511000</v>
       </c>
       <c r="F89" s="3">
-        <v>18731600</v>
+        <v>19540100</v>
       </c>
       <c r="G89" s="3">
-        <v>18910100</v>
+        <v>18604300</v>
       </c>
       <c r="H89" s="3">
-        <v>14123500</v>
+        <v>18781500</v>
       </c>
       <c r="I89" s="3">
-        <v>14798200</v>
+        <v>14027500</v>
       </c>
       <c r="J89" s="3">
+        <v>14697500</v>
+      </c>
+      <c r="K89" s="3">
         <v>15476000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>13642200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13148100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7628000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9773500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11553100</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-6800600</v>
+        <v>-4559500</v>
       </c>
       <c r="E91" s="3">
-        <v>-6308800</v>
+        <v>-6754400</v>
       </c>
       <c r="F91" s="3">
-        <v>-5889900</v>
+        <v>-6265900</v>
       </c>
       <c r="G91" s="3">
-        <v>-5638500</v>
+        <v>-5849800</v>
       </c>
       <c r="H91" s="3">
-        <v>-5498200</v>
+        <v>-5600200</v>
       </c>
       <c r="I91" s="3">
-        <v>-5350200</v>
+        <v>-5460800</v>
       </c>
       <c r="J91" s="3">
+        <v>-5313800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-6838700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7887200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7601600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5385100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4383900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4567600</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-412400</v>
+        <v>-6616000</v>
       </c>
       <c r="E94" s="3">
-        <v>-7473100</v>
+        <v>-409600</v>
       </c>
       <c r="F94" s="3">
-        <v>-10078000</v>
+        <v>-7422200</v>
       </c>
       <c r="G94" s="3">
-        <v>-8800600</v>
+        <v>-10009400</v>
       </c>
       <c r="H94" s="3">
-        <v>-10029000</v>
+        <v>-8740700</v>
       </c>
       <c r="I94" s="3">
-        <v>-10708000</v>
+        <v>-9960800</v>
       </c>
       <c r="J94" s="3">
+        <v>-10635200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-9165100</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13735600</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P94" s="3">
         <v>7383800</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2702800</v>
+        <v>-2626100</v>
       </c>
       <c r="E96" s="3">
-        <v>-2692000</v>
+        <v>-2684500</v>
       </c>
       <c r="F96" s="3">
-        <v>-2640800</v>
+        <v>-2673700</v>
       </c>
       <c r="G96" s="3">
-        <v>-2498300</v>
+        <v>-2622900</v>
       </c>
       <c r="H96" s="3">
-        <v>-4422000</v>
+        <v>-2481300</v>
       </c>
       <c r="I96" s="3">
-        <v>-4265400</v>
+        <v>-4392000</v>
       </c>
       <c r="J96" s="3">
+        <v>-4236300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-4041200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-4047000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-3900400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-6218000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-5323100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-7453400</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-14613200</v>
+        <v>-17134500</v>
       </c>
       <c r="E100" s="3">
-        <v>-10561100</v>
+        <v>-14513800</v>
       </c>
       <c r="F100" s="3">
-        <v>-16534800</v>
+        <v>-10489300</v>
       </c>
       <c r="G100" s="3">
-        <v>-10175900</v>
+        <v>-16422300</v>
       </c>
       <c r="H100" s="3">
-        <v>4827900</v>
+        <v>-10106700</v>
       </c>
       <c r="I100" s="3">
-        <v>-7871300</v>
+        <v>4795100</v>
       </c>
       <c r="J100" s="3">
+        <v>-7817800</v>
+      </c>
+      <c r="K100" s="3">
         <v>-9897400</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3281800</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P100" s="3">
         <v>-17580500</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>13100</v>
+        <v>-101600</v>
       </c>
       <c r="E101" s="3">
-        <v>80500</v>
+        <v>13000</v>
       </c>
       <c r="F101" s="3">
-        <v>-277500</v>
+        <v>80000</v>
       </c>
       <c r="G101" s="3">
-        <v>-278600</v>
+        <v>-275600</v>
       </c>
       <c r="H101" s="3">
-        <v>12000</v>
+        <v>-276700</v>
       </c>
       <c r="I101" s="3">
-        <v>-471100</v>
+        <v>11900</v>
       </c>
       <c r="J101" s="3">
+        <v>-467900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-340600</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1012000</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3">
         <v>-388200</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>4632000</v>
+        <v>-5959000</v>
       </c>
       <c r="E102" s="3">
-        <v>1720300</v>
+        <v>4600500</v>
       </c>
       <c r="F102" s="3">
-        <v>-8158600</v>
+        <v>1708600</v>
       </c>
       <c r="G102" s="3">
-        <v>-344900</v>
+        <v>-8103100</v>
       </c>
       <c r="H102" s="3">
-        <v>8934400</v>
+        <v>-342600</v>
       </c>
       <c r="I102" s="3">
-        <v>-4252300</v>
+        <v>8873600</v>
       </c>
       <c r="J102" s="3">
+        <v>-4223400</v>
+      </c>
+      <c r="K102" s="3">
         <v>-3927000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2964700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2857300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3192300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>559300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>968300</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>39680100</v>
+        <v>40667700</v>
       </c>
       <c r="E8" s="3">
-        <v>40712100</v>
+        <v>41725500</v>
       </c>
       <c r="F8" s="3">
-        <v>39996700</v>
+        <v>40992300</v>
       </c>
       <c r="G8" s="3">
-        <v>47344400</v>
+        <v>48522800</v>
       </c>
       <c r="H8" s="3">
-        <v>48603400</v>
+        <v>49813200</v>
       </c>
       <c r="I8" s="3">
-        <v>47189800</v>
+        <v>48364500</v>
       </c>
       <c r="J8" s="3">
-        <v>50329300</v>
+        <v>51582000</v>
       </c>
       <c r="K8" s="3">
         <v>51827300</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>26432800</v>
+        <v>27090800</v>
       </c>
       <c r="E9" s="3">
-        <v>26324800</v>
+        <v>26980000</v>
       </c>
       <c r="F9" s="3">
-        <v>25880600</v>
+        <v>26524800</v>
       </c>
       <c r="G9" s="3">
-        <v>32513900</v>
+        <v>33323300</v>
       </c>
       <c r="H9" s="3">
-        <v>33158000</v>
+        <v>33983400</v>
       </c>
       <c r="I9" s="3">
-        <v>32593900</v>
+        <v>33405200</v>
       </c>
       <c r="J9" s="3">
-        <v>35415600</v>
+        <v>36297200</v>
       </c>
       <c r="K9" s="3">
         <v>37622100</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13247200</v>
+        <v>13577000</v>
       </c>
       <c r="E10" s="3">
-        <v>14387400</v>
+        <v>14745500</v>
       </c>
       <c r="F10" s="3">
-        <v>14116100</v>
+        <v>14467500</v>
       </c>
       <c r="G10" s="3">
-        <v>14830400</v>
+        <v>15199600</v>
       </c>
       <c r="H10" s="3">
-        <v>15445400</v>
+        <v>15829800</v>
       </c>
       <c r="I10" s="3">
-        <v>14595900</v>
+        <v>14959200</v>
       </c>
       <c r="J10" s="3">
-        <v>14913700</v>
+        <v>15284900</v>
       </c>
       <c r="K10" s="3">
         <v>14205100</v>
@@ -970,22 +970,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-69200</v>
+        <v>-70900</v>
       </c>
       <c r="E14" s="3">
-        <v>-10034300</v>
+        <v>-10284100</v>
       </c>
       <c r="F14" s="3">
-        <v>87500</v>
+        <v>89700</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>1821000</v>
+        <v>1866300</v>
       </c>
       <c r="I14" s="3">
-        <v>3809500</v>
+        <v>3904300</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>35719300</v>
+        <v>36608400</v>
       </c>
       <c r="E17" s="3">
-        <v>25094900</v>
+        <v>25719600</v>
       </c>
       <c r="F17" s="3">
-        <v>33793500</v>
+        <v>34634700</v>
       </c>
       <c r="G17" s="3">
-        <v>41801500</v>
+        <v>42842000</v>
       </c>
       <c r="H17" s="3">
-        <v>44173600</v>
+        <v>45273200</v>
       </c>
       <c r="I17" s="3">
-        <v>48217600</v>
+        <v>49417800</v>
       </c>
       <c r="J17" s="3">
-        <v>45683400</v>
+        <v>46820500</v>
       </c>
       <c r="K17" s="3">
         <v>47774100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3960800</v>
+        <v>4059400</v>
       </c>
       <c r="E18" s="3">
-        <v>15617200</v>
+        <v>16005900</v>
       </c>
       <c r="F18" s="3">
-        <v>6203200</v>
+        <v>6357600</v>
       </c>
       <c r="G18" s="3">
-        <v>5542900</v>
+        <v>5680900</v>
       </c>
       <c r="H18" s="3">
-        <v>4429800</v>
+        <v>4540100</v>
       </c>
       <c r="I18" s="3">
-        <v>-1027700</v>
+        <v>-1053300</v>
       </c>
       <c r="J18" s="3">
-        <v>4645900</v>
+        <v>4761600</v>
       </c>
       <c r="K18" s="3">
         <v>4053200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>759700</v>
+        <v>778600</v>
       </c>
       <c r="E20" s="3">
-        <v>1168200</v>
+        <v>1197300</v>
       </c>
       <c r="F20" s="3">
-        <v>756500</v>
+        <v>775300</v>
       </c>
       <c r="G20" s="3">
-        <v>1920400</v>
+        <v>1968200</v>
       </c>
       <c r="H20" s="3">
-        <v>-581400</v>
+        <v>-595900</v>
       </c>
       <c r="I20" s="3">
-        <v>-50800</v>
+        <v>-52100</v>
       </c>
       <c r="J20" s="3">
-        <v>728400</v>
+        <v>746500</v>
       </c>
       <c r="K20" s="3">
         <v>280700</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>15904000</v>
+        <v>16370500</v>
       </c>
       <c r="E21" s="3">
-        <v>31409700</v>
+        <v>32283800</v>
       </c>
       <c r="F21" s="3">
-        <v>21827700</v>
+        <v>22464900</v>
       </c>
       <c r="G21" s="3">
-        <v>22606200</v>
+        <v>23264500</v>
       </c>
       <c r="H21" s="3">
-        <v>19069700</v>
+        <v>19640500</v>
       </c>
       <c r="I21" s="3">
-        <v>9440200</v>
+        <v>9741600</v>
       </c>
       <c r="J21" s="3">
-        <v>16552400</v>
+        <v>17035000</v>
       </c>
       <c r="K21" s="3">
         <v>16468500</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2969800</v>
+        <v>3043700</v>
       </c>
       <c r="E22" s="3">
-        <v>2656400</v>
+        <v>2722500</v>
       </c>
       <c r="F22" s="3">
-        <v>2475900</v>
+        <v>2537500</v>
       </c>
       <c r="G22" s="3">
-        <v>2765500</v>
+        <v>2834300</v>
       </c>
       <c r="H22" s="3">
-        <v>2989200</v>
+        <v>3063600</v>
       </c>
       <c r="I22" s="3">
-        <v>1745300</v>
+        <v>1788800</v>
       </c>
       <c r="J22" s="3">
-        <v>1183400</v>
+        <v>1212800</v>
       </c>
       <c r="K22" s="3">
         <v>1295900</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1750700</v>
+        <v>1794300</v>
       </c>
       <c r="E23" s="3">
-        <v>14129100</v>
+        <v>14480800</v>
       </c>
       <c r="F23" s="3">
-        <v>4483800</v>
+        <v>4595400</v>
       </c>
       <c r="G23" s="3">
-        <v>4697800</v>
+        <v>4814700</v>
       </c>
       <c r="H23" s="3">
-        <v>859200</v>
+        <v>880500</v>
       </c>
       <c r="I23" s="3">
-        <v>-2823900</v>
+        <v>-2894200</v>
       </c>
       <c r="J23" s="3">
-        <v>4191000</v>
+        <v>4295300</v>
       </c>
       <c r="K23" s="3">
         <v>3038000</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>54000</v>
+        <v>55400</v>
       </c>
       <c r="E24" s="3">
-        <v>531700</v>
+        <v>544900</v>
       </c>
       <c r="F24" s="3">
-        <v>1687000</v>
+        <v>1729000</v>
       </c>
       <c r="G24" s="3">
-        <v>4175800</v>
+        <v>4279800</v>
       </c>
       <c r="H24" s="3">
-        <v>1350900</v>
+        <v>1384500</v>
       </c>
       <c r="I24" s="3">
-        <v>1616700</v>
+        <v>1657000</v>
       </c>
       <c r="J24" s="3">
-        <v>-949900</v>
+        <v>-973600</v>
       </c>
       <c r="K24" s="3">
         <v>5183700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1696700</v>
+        <v>1738900</v>
       </c>
       <c r="E26" s="3">
-        <v>13597400</v>
+        <v>13935800</v>
       </c>
       <c r="F26" s="3">
-        <v>2796900</v>
+        <v>2866500</v>
       </c>
       <c r="G26" s="3">
-        <v>522000</v>
+        <v>535000</v>
       </c>
       <c r="H26" s="3">
-        <v>-491700</v>
+        <v>-504000</v>
       </c>
       <c r="I26" s="3">
-        <v>-4440600</v>
+        <v>-4551100</v>
       </c>
       <c r="J26" s="3">
-        <v>5140900</v>
+        <v>5268900</v>
       </c>
       <c r="K26" s="3">
         <v>-2145700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1302200</v>
+        <v>1334700</v>
       </c>
       <c r="E27" s="3">
-        <v>13060300</v>
+        <v>13385300</v>
       </c>
       <c r="F27" s="3">
-        <v>2217600</v>
+        <v>2272800</v>
       </c>
       <c r="G27" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="H27" s="3">
-        <v>-994200</v>
+        <v>-1019000</v>
       </c>
       <c r="I27" s="3">
-        <v>-4846900</v>
+        <v>-4967600</v>
       </c>
       <c r="J27" s="3">
-        <v>4763700</v>
+        <v>4882300</v>
       </c>
       <c r="K27" s="3">
         <v>-2382900</v>
@@ -1590,13 +1590,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-70200</v>
+        <v>-72000</v>
       </c>
       <c r="E29" s="3">
-        <v>-266900</v>
+        <v>-273600</v>
       </c>
       <c r="F29" s="3">
-        <v>199900</v>
+        <v>204900</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-3820300</v>
+        <v>-3915400</v>
       </c>
       <c r="J29" s="3">
-        <v>-2127900</v>
+        <v>-2180900</v>
       </c>
       <c r="K29" s="3">
         <v>-4468800</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-759700</v>
+        <v>-778600</v>
       </c>
       <c r="E32" s="3">
-        <v>-1168200</v>
+        <v>-1197300</v>
       </c>
       <c r="F32" s="3">
-        <v>-756500</v>
+        <v>-775300</v>
       </c>
       <c r="G32" s="3">
-        <v>-1920400</v>
+        <v>-1968200</v>
       </c>
       <c r="H32" s="3">
-        <v>581400</v>
+        <v>595900</v>
       </c>
       <c r="I32" s="3">
-        <v>50800</v>
+        <v>52100</v>
       </c>
       <c r="J32" s="3">
-        <v>-728400</v>
+        <v>-746500</v>
       </c>
       <c r="K32" s="3">
         <v>-280700</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1232000</v>
+        <v>1262700</v>
       </c>
       <c r="E33" s="3">
-        <v>12793300</v>
+        <v>13111800</v>
       </c>
       <c r="F33" s="3">
-        <v>2417500</v>
+        <v>2477700</v>
       </c>
       <c r="G33" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="H33" s="3">
-        <v>-994200</v>
+        <v>-1019000</v>
       </c>
       <c r="I33" s="3">
-        <v>-8667200</v>
+        <v>-8883000</v>
       </c>
       <c r="J33" s="3">
-        <v>2635800</v>
+        <v>2701400</v>
       </c>
       <c r="K33" s="3">
         <v>-6851800</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1232000</v>
+        <v>1262700</v>
       </c>
       <c r="E35" s="3">
-        <v>12793300</v>
+        <v>13111800</v>
       </c>
       <c r="F35" s="3">
-        <v>2417500</v>
+        <v>2477700</v>
       </c>
       <c r="G35" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="H35" s="3">
-        <v>-994200</v>
+        <v>-1019000</v>
       </c>
       <c r="I35" s="3">
-        <v>-8667200</v>
+        <v>-8883000</v>
       </c>
       <c r="J35" s="3">
-        <v>2635800</v>
+        <v>2701400</v>
       </c>
       <c r="K35" s="3">
         <v>-6851800</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4483800</v>
+        <v>4595400</v>
       </c>
       <c r="E41" s="3">
-        <v>10758400</v>
+        <v>11026200</v>
       </c>
       <c r="F41" s="3">
-        <v>10500100</v>
+        <v>10761400</v>
       </c>
       <c r="G41" s="3">
-        <v>6290800</v>
+        <v>6447300</v>
       </c>
       <c r="H41" s="3">
-        <v>12271300</v>
+        <v>12576800</v>
       </c>
       <c r="I41" s="3">
-        <v>12364300</v>
+        <v>12672100</v>
       </c>
       <c r="J41" s="3">
-        <v>5051200</v>
+        <v>5176900</v>
       </c>
       <c r="K41" s="3">
         <v>9613400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>7701100</v>
+        <v>7892800</v>
       </c>
       <c r="E42" s="3">
-        <v>9474500</v>
+        <v>9710300</v>
       </c>
       <c r="F42" s="3">
-        <v>8571000</v>
+        <v>8784400</v>
       </c>
       <c r="G42" s="3">
-        <v>9898100</v>
+        <v>10144500</v>
       </c>
       <c r="H42" s="3">
-        <v>10040800</v>
+        <v>10290700</v>
       </c>
       <c r="I42" s="3">
-        <v>16435300</v>
+        <v>16844400</v>
       </c>
       <c r="J42" s="3">
-        <v>9504800</v>
+        <v>9741300</v>
       </c>
       <c r="K42" s="3">
         <v>6659200</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8488900</v>
+        <v>8700200</v>
       </c>
       <c r="E43" s="3">
-        <v>10447100</v>
+        <v>10707200</v>
       </c>
       <c r="F43" s="3">
-        <v>10842700</v>
+        <v>11112600</v>
       </c>
       <c r="G43" s="3">
-        <v>10845900</v>
+        <v>11115900</v>
       </c>
       <c r="H43" s="3">
-        <v>11128000</v>
+        <v>11405000</v>
       </c>
       <c r="I43" s="3">
-        <v>11922300</v>
+        <v>12219000</v>
       </c>
       <c r="J43" s="3">
-        <v>9455000</v>
+        <v>9690400</v>
       </c>
       <c r="K43" s="3">
         <v>8926800</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>613800</v>
+        <v>629100</v>
       </c>
       <c r="E44" s="3">
-        <v>1033100</v>
+        <v>1058900</v>
       </c>
       <c r="F44" s="3">
-        <v>903500</v>
+        <v>926000</v>
       </c>
       <c r="G44" s="3">
-        <v>730600</v>
+        <v>748700</v>
       </c>
       <c r="H44" s="3">
-        <v>646300</v>
+        <v>662300</v>
       </c>
       <c r="I44" s="3">
-        <v>771600</v>
+        <v>790800</v>
       </c>
       <c r="J44" s="3">
-        <v>627900</v>
+        <v>643500</v>
       </c>
       <c r="K44" s="3">
         <v>626700</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>880800</v>
+        <v>902700</v>
       </c>
       <c r="E45" s="3">
-        <v>1423300</v>
+        <v>1458700</v>
       </c>
       <c r="F45" s="3">
-        <v>1385500</v>
+        <v>1419900</v>
       </c>
       <c r="G45" s="3">
-        <v>1427600</v>
+        <v>1463100</v>
       </c>
       <c r="H45" s="3">
-        <v>1842600</v>
+        <v>1888500</v>
       </c>
       <c r="I45" s="3">
-        <v>1536800</v>
+        <v>1575000</v>
       </c>
       <c r="J45" s="3">
-        <v>1439500</v>
+        <v>1475300</v>
       </c>
       <c r="K45" s="3">
         <v>1966200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>22168400</v>
+        <v>22720200</v>
       </c>
       <c r="E46" s="3">
-        <v>33136400</v>
+        <v>33961200</v>
       </c>
       <c r="F46" s="3">
-        <v>29803500</v>
+        <v>30545400</v>
       </c>
       <c r="G46" s="3">
-        <v>29192900</v>
+        <v>29919600</v>
       </c>
       <c r="H46" s="3">
-        <v>35929000</v>
+        <v>36823300</v>
       </c>
       <c r="I46" s="3">
-        <v>43030200</v>
+        <v>44101300</v>
       </c>
       <c r="J46" s="3">
-        <v>26078400</v>
+        <v>26727500</v>
       </c>
       <c r="K46" s="3">
         <v>27792300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>13784300</v>
+        <v>14127400</v>
       </c>
       <c r="E47" s="3">
-        <v>15213000</v>
+        <v>15591700</v>
       </c>
       <c r="F47" s="3">
-        <v>9004400</v>
+        <v>9228500</v>
       </c>
       <c r="G47" s="3">
-        <v>7795100</v>
+        <v>7989100</v>
       </c>
       <c r="H47" s="3">
-        <v>9040100</v>
+        <v>9265100</v>
       </c>
       <c r="I47" s="3">
-        <v>10798400</v>
+        <v>11067100</v>
       </c>
       <c r="J47" s="3">
-        <v>10556300</v>
+        <v>10819000</v>
       </c>
       <c r="K47" s="3">
         <v>12149700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>30798900</v>
+        <v>31565500</v>
       </c>
       <c r="E48" s="3">
-        <v>41058000</v>
+        <v>42079900</v>
       </c>
       <c r="F48" s="3">
-        <v>44096900</v>
+        <v>45194500</v>
       </c>
       <c r="G48" s="3">
-        <v>44571300</v>
+        <v>45680700</v>
       </c>
       <c r="H48" s="3">
-        <v>43350100</v>
+        <v>44429200</v>
       </c>
       <c r="I48" s="3">
-        <v>29645800</v>
+        <v>30383700</v>
       </c>
       <c r="J48" s="3">
-        <v>30610800</v>
+        <v>31372800</v>
       </c>
       <c r="K48" s="3">
         <v>32865000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>41987400</v>
+        <v>43032500</v>
       </c>
       <c r="E49" s="3">
-        <v>51016600</v>
+        <v>52286500</v>
       </c>
       <c r="F49" s="3">
-        <v>57540800</v>
+        <v>58973100</v>
       </c>
       <c r="G49" s="3">
-        <v>57870400</v>
+        <v>59310900</v>
       </c>
       <c r="H49" s="3">
-        <v>58367500</v>
+        <v>59820400</v>
       </c>
       <c r="I49" s="3">
-        <v>44314100</v>
+        <v>45417100</v>
       </c>
       <c r="J49" s="3">
-        <v>46747800</v>
+        <v>47911500</v>
       </c>
       <c r="K49" s="3">
         <v>50292000</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>47260100</v>
+        <v>48436500</v>
       </c>
       <c r="E52" s="3">
-        <v>27647500</v>
+        <v>28335700</v>
       </c>
       <c r="F52" s="3">
-        <v>27071500</v>
+        <v>27745400</v>
       </c>
       <c r="G52" s="3">
-        <v>28146800</v>
+        <v>28847400</v>
       </c>
       <c r="H52" s="3">
-        <v>35052500</v>
+        <v>35925000</v>
       </c>
       <c r="I52" s="3">
-        <v>26602500</v>
+        <v>27264700</v>
       </c>
       <c r="J52" s="3">
-        <v>43368500</v>
+        <v>44448000</v>
       </c>
       <c r="K52" s="3">
         <v>45212700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>155999000</v>
+        <v>159882000</v>
       </c>
       <c r="E54" s="3">
-        <v>168072000</v>
+        <v>172255000</v>
       </c>
       <c r="F54" s="3">
-        <v>166481000</v>
+        <v>170625000</v>
       </c>
       <c r="G54" s="3">
-        <v>167577000</v>
+        <v>171748000</v>
       </c>
       <c r="H54" s="3">
-        <v>181739000</v>
+        <v>186263000</v>
       </c>
       <c r="I54" s="3">
-        <v>154391000</v>
+        <v>158234000</v>
       </c>
       <c r="J54" s="3">
-        <v>157362000</v>
+        <v>161279000</v>
       </c>
       <c r="K54" s="3">
         <v>168312000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6491800</v>
+        <v>6653400</v>
       </c>
       <c r="E57" s="3">
-        <v>8635900</v>
+        <v>8850800</v>
       </c>
       <c r="F57" s="3">
-        <v>7961500</v>
+        <v>8159700</v>
       </c>
       <c r="G57" s="3">
-        <v>7321700</v>
+        <v>7504000</v>
       </c>
       <c r="H57" s="3">
-        <v>7291500</v>
+        <v>7473000</v>
       </c>
       <c r="I57" s="3">
-        <v>7097000</v>
+        <v>7273600</v>
       </c>
       <c r="J57" s="3">
-        <v>6713300</v>
+        <v>6880400</v>
       </c>
       <c r="K57" s="3">
         <v>6774500</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9357800</v>
+        <v>9590700</v>
       </c>
       <c r="E58" s="3">
-        <v>15909000</v>
+        <v>16305000</v>
       </c>
       <c r="F58" s="3">
-        <v>12926300</v>
+        <v>13248000</v>
       </c>
       <c r="G58" s="3">
-        <v>9173000</v>
+        <v>9401300</v>
       </c>
       <c r="H58" s="3">
-        <v>12942500</v>
+        <v>13264600</v>
       </c>
       <c r="I58" s="3">
-        <v>4614600</v>
+        <v>4729500</v>
       </c>
       <c r="J58" s="3">
-        <v>11186300</v>
+        <v>11464800</v>
       </c>
       <c r="K58" s="3">
         <v>13112700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9312400</v>
+        <v>9544200</v>
       </c>
       <c r="E59" s="3">
-        <v>12830100</v>
+        <v>13149400</v>
       </c>
       <c r="F59" s="3">
-        <v>15474500</v>
+        <v>15859700</v>
       </c>
       <c r="G59" s="3">
-        <v>14533300</v>
+        <v>14895000</v>
       </c>
       <c r="H59" s="3">
-        <v>15845200</v>
+        <v>16239600</v>
       </c>
       <c r="I59" s="3">
-        <v>15871200</v>
+        <v>16266200</v>
       </c>
       <c r="J59" s="3">
-        <v>24273600</v>
+        <v>24877800</v>
       </c>
       <c r="K59" s="3">
         <v>26236300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>25161900</v>
+        <v>25788300</v>
       </c>
       <c r="E60" s="3">
-        <v>37374900</v>
+        <v>38305200</v>
       </c>
       <c r="F60" s="3">
-        <v>36362300</v>
+        <v>37267400</v>
       </c>
       <c r="G60" s="3">
-        <v>31028000</v>
+        <v>31800300</v>
       </c>
       <c r="H60" s="3">
-        <v>36079200</v>
+        <v>36977200</v>
       </c>
       <c r="I60" s="3">
-        <v>27582700</v>
+        <v>28269300</v>
       </c>
       <c r="J60" s="3">
-        <v>42173200</v>
+        <v>43223000</v>
       </c>
       <c r="K60" s="3">
         <v>46123500</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>52228100</v>
+        <v>53528100</v>
       </c>
       <c r="E61" s="3">
-        <v>55838700</v>
+        <v>57228600</v>
       </c>
       <c r="F61" s="3">
-        <v>62822200</v>
+        <v>64385900</v>
       </c>
       <c r="G61" s="3">
-        <v>64055300</v>
+        <v>65649700</v>
       </c>
       <c r="H61" s="3">
-        <v>68029000</v>
+        <v>69722300</v>
       </c>
       <c r="I61" s="3">
-        <v>52613900</v>
+        <v>53923500</v>
       </c>
       <c r="J61" s="3">
-        <v>35263200</v>
+        <v>36141000</v>
       </c>
       <c r="K61" s="3">
         <v>37232600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5212200</v>
+        <v>5342000</v>
       </c>
       <c r="E62" s="3">
-        <v>5171100</v>
+        <v>5299900</v>
       </c>
       <c r="F62" s="3">
-        <v>5617500</v>
+        <v>5757300</v>
       </c>
       <c r="G62" s="3">
-        <v>10011600</v>
+        <v>10260800</v>
       </c>
       <c r="H62" s="3">
-        <v>9952200</v>
+        <v>10199900</v>
       </c>
       <c r="I62" s="3">
-        <v>5629400</v>
+        <v>5769500</v>
       </c>
       <c r="J62" s="3">
-        <v>5781700</v>
+        <v>5925700</v>
       </c>
       <c r="K62" s="3">
         <v>4741900</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>91193800</v>
+        <v>93463700</v>
       </c>
       <c r="E66" s="3">
-        <v>99556200</v>
+        <v>102034000</v>
       </c>
       <c r="F66" s="3">
-        <v>107277000</v>
+        <v>109947000</v>
       </c>
       <c r="G66" s="3">
-        <v>107269000</v>
+        <v>109939000</v>
       </c>
       <c r="H66" s="3">
-        <v>115373000</v>
+        <v>118245000</v>
       </c>
       <c r="I66" s="3">
-        <v>87152000</v>
+        <v>89321300</v>
       </c>
       <c r="J66" s="3">
-        <v>84263300</v>
+        <v>86360700</v>
       </c>
       <c r="K66" s="3">
         <v>89750800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>64805300</v>
+        <v>66418300</v>
       </c>
       <c r="E76" s="3">
-        <v>68515300</v>
+        <v>70220700</v>
       </c>
       <c r="F76" s="3">
-        <v>59204000</v>
+        <v>60677700</v>
       </c>
       <c r="G76" s="3">
-        <v>60307400</v>
+        <v>61808500</v>
       </c>
       <c r="H76" s="3">
-        <v>66365800</v>
+        <v>68017700</v>
       </c>
       <c r="I76" s="3">
-        <v>67239000</v>
+        <v>68912700</v>
       </c>
       <c r="J76" s="3">
-        <v>73098500</v>
+        <v>74918100</v>
       </c>
       <c r="K76" s="3">
         <v>78560800</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1232000</v>
+        <v>1262700</v>
       </c>
       <c r="E81" s="3">
-        <v>12793300</v>
+        <v>13111800</v>
       </c>
       <c r="F81" s="3">
-        <v>2417500</v>
+        <v>2477700</v>
       </c>
       <c r="G81" s="3">
-        <v>63800</v>
+        <v>65300</v>
       </c>
       <c r="H81" s="3">
-        <v>-994200</v>
+        <v>-1019000</v>
       </c>
       <c r="I81" s="3">
-        <v>-8667200</v>
+        <v>-8883000</v>
       </c>
       <c r="J81" s="3">
-        <v>2635800</v>
+        <v>2701400</v>
       </c>
       <c r="K81" s="3">
         <v>-6851800</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11254400</v>
+        <v>11534500</v>
       </c>
       <c r="E83" s="3">
-        <v>14717000</v>
+        <v>15083300</v>
       </c>
       <c r="F83" s="3">
-        <v>14962300</v>
+        <v>15334700</v>
       </c>
       <c r="G83" s="3">
-        <v>15239000</v>
+        <v>15618300</v>
       </c>
       <c r="H83" s="3">
-        <v>15317800</v>
+        <v>15699100</v>
       </c>
       <c r="I83" s="3">
-        <v>10585500</v>
+        <v>10848900</v>
       </c>
       <c r="J83" s="3">
-        <v>11249000</v>
+        <v>11529000</v>
       </c>
       <c r="K83" s="3">
         <v>12062700</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>17893100</v>
+        <v>18338500</v>
       </c>
       <c r="E89" s="3">
-        <v>19511000</v>
+        <v>19996600</v>
       </c>
       <c r="F89" s="3">
-        <v>19540100</v>
+        <v>20026500</v>
       </c>
       <c r="G89" s="3">
-        <v>18604300</v>
+        <v>19067300</v>
       </c>
       <c r="H89" s="3">
-        <v>18781500</v>
+        <v>19249000</v>
       </c>
       <c r="I89" s="3">
-        <v>14027500</v>
+        <v>14376600</v>
       </c>
       <c r="J89" s="3">
-        <v>14697500</v>
+        <v>15063400</v>
       </c>
       <c r="K89" s="3">
         <v>15476000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4559500</v>
+        <v>-4673000</v>
       </c>
       <c r="E91" s="3">
-        <v>-6754400</v>
+        <v>-6922500</v>
       </c>
       <c r="F91" s="3">
-        <v>-6265900</v>
+        <v>-6421900</v>
       </c>
       <c r="G91" s="3">
-        <v>-5849800</v>
+        <v>-5995400</v>
       </c>
       <c r="H91" s="3">
-        <v>-5600200</v>
+        <v>-5739600</v>
       </c>
       <c r="I91" s="3">
-        <v>-5460800</v>
+        <v>-5596700</v>
       </c>
       <c r="J91" s="3">
-        <v>-5313800</v>
+        <v>-5446100</v>
       </c>
       <c r="K91" s="3">
         <v>-6838700</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6616000</v>
+        <v>-6780700</v>
       </c>
       <c r="E94" s="3">
-        <v>-409600</v>
+        <v>-419800</v>
       </c>
       <c r="F94" s="3">
-        <v>-7422200</v>
+        <v>-7607000</v>
       </c>
       <c r="G94" s="3">
-        <v>-10009400</v>
+        <v>-10258600</v>
       </c>
       <c r="H94" s="3">
-        <v>-8740700</v>
+        <v>-8958300</v>
       </c>
       <c r="I94" s="3">
-        <v>-9960800</v>
+        <v>-10208700</v>
       </c>
       <c r="J94" s="3">
-        <v>-10635200</v>
+        <v>-10899900</v>
       </c>
       <c r="K94" s="3">
         <v>-9165100</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2626100</v>
+        <v>-2691500</v>
       </c>
       <c r="E96" s="3">
-        <v>-2684500</v>
+        <v>-2751300</v>
       </c>
       <c r="F96" s="3">
-        <v>-2673700</v>
+        <v>-2740200</v>
       </c>
       <c r="G96" s="3">
-        <v>-2622900</v>
+        <v>-2688100</v>
       </c>
       <c r="H96" s="3">
-        <v>-2481300</v>
+        <v>-2543000</v>
       </c>
       <c r="I96" s="3">
-        <v>-4392000</v>
+        <v>-4501300</v>
       </c>
       <c r="J96" s="3">
-        <v>-4236300</v>
+        <v>-4341800</v>
       </c>
       <c r="K96" s="3">
         <v>-4041200</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-17134500</v>
+        <v>-17561000</v>
       </c>
       <c r="E100" s="3">
-        <v>-14513800</v>
+        <v>-14875100</v>
       </c>
       <c r="F100" s="3">
-        <v>-10489300</v>
+        <v>-10750400</v>
       </c>
       <c r="G100" s="3">
-        <v>-16422300</v>
+        <v>-16831100</v>
       </c>
       <c r="H100" s="3">
-        <v>-10106700</v>
+        <v>-10358300</v>
       </c>
       <c r="I100" s="3">
-        <v>4795100</v>
+        <v>4914400</v>
       </c>
       <c r="J100" s="3">
-        <v>-7817800</v>
+        <v>-8012400</v>
       </c>
       <c r="K100" s="3">
         <v>-9897400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-101600</v>
+        <v>-104100</v>
       </c>
       <c r="E101" s="3">
-        <v>13000</v>
+        <v>13300</v>
       </c>
       <c r="F101" s="3">
-        <v>80000</v>
+        <v>82000</v>
       </c>
       <c r="G101" s="3">
-        <v>-275600</v>
+        <v>-282400</v>
       </c>
       <c r="H101" s="3">
-        <v>-276700</v>
+        <v>-283500</v>
       </c>
       <c r="I101" s="3">
-        <v>11900</v>
+        <v>12200</v>
       </c>
       <c r="J101" s="3">
-        <v>-467900</v>
+        <v>-479600</v>
       </c>
       <c r="K101" s="3">
         <v>-340600</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-5959000</v>
+        <v>-6107300</v>
       </c>
       <c r="E102" s="3">
-        <v>4600500</v>
+        <v>4715100</v>
       </c>
       <c r="F102" s="3">
-        <v>1708600</v>
+        <v>1751100</v>
       </c>
       <c r="G102" s="3">
-        <v>-8103100</v>
+        <v>-8304800</v>
       </c>
       <c r="H102" s="3">
-        <v>-342600</v>
+        <v>-351100</v>
       </c>
       <c r="I102" s="3">
-        <v>8873600</v>
+        <v>9094500</v>
       </c>
       <c r="J102" s="3">
-        <v>-4223400</v>
+        <v>-4328500</v>
       </c>
       <c r="K102" s="3">
         <v>-3927000</v>

--- a/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>40667700</v>
+        <v>39612700</v>
       </c>
       <c r="E8" s="3">
-        <v>41725500</v>
+        <v>40930000</v>
       </c>
       <c r="F8" s="3">
-        <v>40992300</v>
+        <v>41113100</v>
       </c>
       <c r="G8" s="3">
-        <v>48522800</v>
+        <v>51419000</v>
       </c>
       <c r="H8" s="3">
-        <v>49813200</v>
+        <v>49422000</v>
       </c>
       <c r="I8" s="3">
-        <v>48364500</v>
+        <v>49007900</v>
       </c>
       <c r="J8" s="3">
-        <v>51582000</v>
+        <v>57374600</v>
       </c>
       <c r="K8" s="3">
         <v>51827300</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>27090800</v>
+        <v>26388000</v>
       </c>
       <c r="E9" s="3">
-        <v>26980000</v>
+        <v>26465700</v>
       </c>
       <c r="F9" s="3">
-        <v>26524800</v>
+        <v>26603000</v>
       </c>
       <c r="G9" s="3">
-        <v>33323300</v>
+        <v>35312200</v>
       </c>
       <c r="H9" s="3">
-        <v>33983400</v>
+        <v>33716500</v>
       </c>
       <c r="I9" s="3">
-        <v>33405200</v>
+        <v>33849600</v>
       </c>
       <c r="J9" s="3">
-        <v>36297200</v>
+        <v>40373300</v>
       </c>
       <c r="K9" s="3">
         <v>37622100</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13577000</v>
+        <v>13224700</v>
       </c>
       <c r="E10" s="3">
-        <v>14745500</v>
+        <v>14464400</v>
       </c>
       <c r="F10" s="3">
-        <v>14467500</v>
+        <v>14510100</v>
       </c>
       <c r="G10" s="3">
-        <v>15199600</v>
+        <v>16106800</v>
       </c>
       <c r="H10" s="3">
-        <v>15829800</v>
+        <v>15705500</v>
       </c>
       <c r="I10" s="3">
-        <v>14959200</v>
+        <v>15158200</v>
       </c>
       <c r="J10" s="3">
-        <v>15284900</v>
+        <v>17001400</v>
       </c>
       <c r="K10" s="3">
         <v>14205100</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-70900</v>
+        <v>-457400</v>
       </c>
       <c r="E14" s="3">
-        <v>-10284100</v>
+        <v>-10088000</v>
       </c>
       <c r="F14" s="3">
-        <v>89700</v>
+        <v>-50000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-1566900</v>
       </c>
       <c r="H14" s="3">
-        <v>1866300</v>
+        <v>-3207700</v>
       </c>
       <c r="I14" s="3">
-        <v>3904300</v>
+        <v>3956200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>650500</v>
       </c>
       <c r="K14" s="3">
         <v>-1387300</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>5300500</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>5624700</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>8552500</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>11956600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>11487900</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>10993300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>12823700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>36608400</v>
+        <v>35864700</v>
       </c>
       <c r="E17" s="3">
-        <v>25719600</v>
+        <v>36046300</v>
       </c>
       <c r="F17" s="3">
-        <v>34634700</v>
+        <v>35232200</v>
       </c>
       <c r="G17" s="3">
-        <v>42842000</v>
+        <v>47408500</v>
       </c>
       <c r="H17" s="3">
-        <v>45273200</v>
+        <v>45439600</v>
       </c>
       <c r="I17" s="3">
-        <v>49417800</v>
+        <v>45098800</v>
       </c>
       <c r="J17" s="3">
-        <v>46820500</v>
+        <v>51435300</v>
       </c>
       <c r="K17" s="3">
         <v>47774100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4059400</v>
+        <v>3748000</v>
       </c>
       <c r="E18" s="3">
-        <v>16005900</v>
+        <v>4883700</v>
       </c>
       <c r="F18" s="3">
-        <v>6357600</v>
+        <v>5880900</v>
       </c>
       <c r="G18" s="3">
-        <v>5680900</v>
+        <v>4010600</v>
       </c>
       <c r="H18" s="3">
-        <v>4540100</v>
+        <v>3982400</v>
       </c>
       <c r="I18" s="3">
-        <v>-1053300</v>
+        <v>3909100</v>
       </c>
       <c r="J18" s="3">
-        <v>4761600</v>
+        <v>5939400</v>
       </c>
       <c r="K18" s="3">
         <v>4053200</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>778600</v>
+        <v>545900</v>
       </c>
       <c r="E20" s="3">
-        <v>1197300</v>
+        <v>-1041900</v>
       </c>
       <c r="F20" s="3">
-        <v>775300</v>
+        <v>-468800</v>
       </c>
       <c r="G20" s="3">
-        <v>1968200</v>
+        <v>-1671400</v>
       </c>
       <c r="H20" s="3">
-        <v>-595900</v>
+        <v>4191200</v>
       </c>
       <c r="I20" s="3">
-        <v>-52100</v>
+        <v>1717200</v>
       </c>
       <c r="J20" s="3">
-        <v>746500</v>
+        <v>-45600</v>
       </c>
       <c r="K20" s="3">
         <v>280700</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>16370500</v>
+        <v>8502500</v>
       </c>
       <c r="E21" s="3">
-        <v>32283800</v>
+        <v>11550400</v>
       </c>
       <c r="F21" s="3">
-        <v>22464900</v>
+        <v>14902200</v>
       </c>
       <c r="G21" s="3">
-        <v>23264500</v>
+        <v>17638500</v>
       </c>
       <c r="H21" s="3">
-        <v>19640500</v>
+        <v>11279100</v>
       </c>
       <c r="I21" s="3">
-        <v>9741600</v>
+        <v>13185200</v>
       </c>
       <c r="J21" s="3">
-        <v>17035000</v>
+        <v>18808700</v>
       </c>
       <c r="K21" s="3">
         <v>16468500</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>3043700</v>
+        <v>2538600</v>
       </c>
       <c r="E22" s="3">
-        <v>2722500</v>
+        <v>2061100</v>
       </c>
       <c r="F22" s="3">
-        <v>2537500</v>
+        <v>2069500</v>
       </c>
       <c r="G22" s="3">
-        <v>2834300</v>
+        <v>2434300</v>
       </c>
       <c r="H22" s="3">
-        <v>3063600</v>
+        <v>2397800</v>
       </c>
       <c r="I22" s="3">
-        <v>1788800</v>
+        <v>1654300</v>
       </c>
       <c r="J22" s="3">
-        <v>1212800</v>
+        <v>1414300</v>
       </c>
       <c r="K22" s="3">
         <v>1295900</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1794300</v>
+        <v>1747800</v>
       </c>
       <c r="E23" s="3">
-        <v>14480800</v>
+        <v>14204700</v>
       </c>
       <c r="F23" s="3">
-        <v>4595400</v>
+        <v>4609000</v>
       </c>
       <c r="G23" s="3">
-        <v>4814700</v>
+        <v>5102100</v>
       </c>
       <c r="H23" s="3">
-        <v>880500</v>
+        <v>873600</v>
       </c>
       <c r="I23" s="3">
-        <v>-2894200</v>
+        <v>-2932700</v>
       </c>
       <c r="J23" s="3">
-        <v>4295300</v>
+        <v>4777600</v>
       </c>
       <c r="K23" s="3">
         <v>3038000</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>55400</v>
+        <v>53900</v>
       </c>
       <c r="E24" s="3">
-        <v>544900</v>
+        <v>534600</v>
       </c>
       <c r="F24" s="3">
-        <v>1729000</v>
+        <v>1734100</v>
       </c>
       <c r="G24" s="3">
-        <v>4279800</v>
+        <v>4535200</v>
       </c>
       <c r="H24" s="3">
-        <v>1384500</v>
+        <v>1373600</v>
       </c>
       <c r="I24" s="3">
-        <v>1657000</v>
+        <v>1679000</v>
       </c>
       <c r="J24" s="3">
-        <v>-973600</v>
+        <v>-1082900</v>
       </c>
       <c r="K24" s="3">
         <v>5183700</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1738900</v>
+        <v>1693800</v>
       </c>
       <c r="E26" s="3">
-        <v>13935800</v>
+        <v>13670100</v>
       </c>
       <c r="F26" s="3">
-        <v>2866500</v>
+        <v>2874900</v>
       </c>
       <c r="G26" s="3">
-        <v>535000</v>
+        <v>566900</v>
       </c>
       <c r="H26" s="3">
-        <v>-504000</v>
+        <v>-500000</v>
       </c>
       <c r="I26" s="3">
-        <v>-4551100</v>
+        <v>-4611700</v>
       </c>
       <c r="J26" s="3">
-        <v>5268900</v>
+        <v>5860500</v>
       </c>
       <c r="K26" s="3">
         <v>-2145700</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1334700</v>
+        <v>1229900</v>
       </c>
       <c r="E27" s="3">
-        <v>13385300</v>
+        <v>12861800</v>
       </c>
       <c r="F27" s="3">
-        <v>2272800</v>
+        <v>2485000</v>
       </c>
       <c r="G27" s="3">
-        <v>65300</v>
+        <v>69300</v>
       </c>
       <c r="H27" s="3">
-        <v>-1019000</v>
+        <v>-1011000</v>
       </c>
       <c r="I27" s="3">
-        <v>-4967600</v>
+        <v>-9001100</v>
       </c>
       <c r="J27" s="3">
-        <v>4882300</v>
+        <v>3004800</v>
       </c>
       <c r="K27" s="3">
         <v>-2382900</v>
@@ -1590,13 +1590,13 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-72000</v>
+        <v>-70100</v>
       </c>
       <c r="E29" s="3">
-        <v>-273600</v>
+        <v>-268400</v>
       </c>
       <c r="F29" s="3">
-        <v>204900</v>
+        <v>205500</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-3915400</v>
+        <v>-3967500</v>
       </c>
       <c r="J29" s="3">
-        <v>-2180900</v>
+        <v>-2425800</v>
       </c>
       <c r="K29" s="3">
         <v>-4468800</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-778600</v>
+        <v>-545900</v>
       </c>
       <c r="E32" s="3">
-        <v>-1197300</v>
+        <v>1041900</v>
       </c>
       <c r="F32" s="3">
-        <v>-775300</v>
+        <v>468800</v>
       </c>
       <c r="G32" s="3">
-        <v>-1968200</v>
+        <v>1671400</v>
       </c>
       <c r="H32" s="3">
-        <v>595900</v>
+        <v>-4191200</v>
       </c>
       <c r="I32" s="3">
-        <v>52100</v>
+        <v>-1717200</v>
       </c>
       <c r="J32" s="3">
-        <v>-746500</v>
+        <v>45600</v>
       </c>
       <c r="K32" s="3">
         <v>-280700</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1262700</v>
+        <v>1229900</v>
       </c>
       <c r="E33" s="3">
-        <v>13111800</v>
+        <v>12861800</v>
       </c>
       <c r="F33" s="3">
-        <v>2477700</v>
+        <v>2485000</v>
       </c>
       <c r="G33" s="3">
-        <v>65300</v>
+        <v>69200</v>
       </c>
       <c r="H33" s="3">
-        <v>-1019000</v>
+        <v>-1011000</v>
       </c>
       <c r="I33" s="3">
-        <v>-8883000</v>
+        <v>-9001100</v>
       </c>
       <c r="J33" s="3">
-        <v>2701400</v>
+        <v>3004800</v>
       </c>
       <c r="K33" s="3">
         <v>-6851800</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1262700</v>
+        <v>1229900</v>
       </c>
       <c r="E35" s="3">
-        <v>13111800</v>
+        <v>12861800</v>
       </c>
       <c r="F35" s="3">
-        <v>2477700</v>
+        <v>2485000</v>
       </c>
       <c r="G35" s="3">
-        <v>65300</v>
+        <v>69200</v>
       </c>
       <c r="H35" s="3">
-        <v>-1019000</v>
+        <v>-1011000</v>
       </c>
       <c r="I35" s="3">
-        <v>-8883000</v>
+        <v>-9001100</v>
       </c>
       <c r="J35" s="3">
-        <v>2701400</v>
+        <v>3004800</v>
       </c>
       <c r="K35" s="3">
         <v>-6851800</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4595400</v>
+        <v>6670600</v>
       </c>
       <c r="E41" s="3">
-        <v>11026200</v>
+        <v>12717300</v>
       </c>
       <c r="F41" s="3">
-        <v>10761400</v>
+        <v>8327000</v>
       </c>
       <c r="G41" s="3">
-        <v>6447300</v>
+        <v>6832200</v>
       </c>
       <c r="H41" s="3">
-        <v>12576800</v>
+        <v>14897800</v>
       </c>
       <c r="I41" s="3">
-        <v>12672100</v>
+        <v>15305300</v>
       </c>
       <c r="J41" s="3">
-        <v>5176900</v>
+        <v>5758300</v>
       </c>
       <c r="K41" s="3">
         <v>9613400</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>7892800</v>
+        <v>4694100</v>
       </c>
       <c r="E42" s="3">
-        <v>9710300</v>
+        <v>7364200</v>
       </c>
       <c r="F42" s="3">
-        <v>8784400</v>
+        <v>8034900</v>
       </c>
       <c r="G42" s="3">
-        <v>10144500</v>
+        <v>7103300</v>
       </c>
       <c r="H42" s="3">
-        <v>10290700</v>
+        <v>6564800</v>
       </c>
       <c r="I42" s="3">
-        <v>16844400</v>
+        <v>13275000</v>
       </c>
       <c r="J42" s="3">
-        <v>9741300</v>
+        <v>9812700</v>
       </c>
       <c r="K42" s="3">
         <v>6659200</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8700200</v>
+        <v>7213300</v>
       </c>
       <c r="E43" s="3">
-        <v>10707200</v>
+        <v>8904800</v>
       </c>
       <c r="F43" s="3">
-        <v>11112600</v>
+        <v>9586800</v>
       </c>
       <c r="G43" s="3">
-        <v>11115900</v>
+        <v>10178400</v>
       </c>
       <c r="H43" s="3">
-        <v>11405000</v>
+        <v>9894500</v>
       </c>
       <c r="I43" s="3">
-        <v>12219000</v>
+        <v>11111100</v>
       </c>
       <c r="J43" s="3">
-        <v>9690400</v>
+        <v>10778600</v>
       </c>
       <c r="K43" s="3">
         <v>8926800</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>629100</v>
+        <v>612800</v>
       </c>
       <c r="E44" s="3">
-        <v>1058900</v>
+        <v>1038700</v>
       </c>
       <c r="F44" s="3">
-        <v>926000</v>
+        <v>928700</v>
       </c>
       <c r="G44" s="3">
-        <v>748700</v>
+        <v>793400</v>
       </c>
       <c r="H44" s="3">
-        <v>662300</v>
+        <v>657100</v>
       </c>
       <c r="I44" s="3">
-        <v>790800</v>
+        <v>801300</v>
       </c>
       <c r="J44" s="3">
-        <v>643500</v>
+        <v>715800</v>
       </c>
       <c r="K44" s="3">
         <v>626700</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>902700</v>
+        <v>22841700</v>
       </c>
       <c r="E45" s="3">
-        <v>1458700</v>
+        <v>2381600</v>
       </c>
       <c r="F45" s="3">
-        <v>1419900</v>
+        <v>2789400</v>
       </c>
       <c r="G45" s="3">
-        <v>1463100</v>
+        <v>7003500</v>
       </c>
       <c r="H45" s="3">
-        <v>1888500</v>
+        <v>3019800</v>
       </c>
       <c r="I45" s="3">
-        <v>1575000</v>
+        <v>2558900</v>
       </c>
       <c r="J45" s="3">
-        <v>1475300</v>
+        <v>18270300</v>
       </c>
       <c r="K45" s="3">
         <v>1966200</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>22720200</v>
+        <v>42679900</v>
       </c>
       <c r="E46" s="3">
-        <v>33961200</v>
+        <v>33313800</v>
       </c>
       <c r="F46" s="3">
-        <v>30545400</v>
+        <v>30635400</v>
       </c>
       <c r="G46" s="3">
-        <v>29919600</v>
+        <v>33180800</v>
       </c>
       <c r="H46" s="3">
-        <v>36823300</v>
+        <v>36081300</v>
       </c>
       <c r="I46" s="3">
-        <v>44101300</v>
+        <v>44428700</v>
       </c>
       <c r="J46" s="3">
-        <v>26727500</v>
+        <v>46755000</v>
       </c>
       <c r="K46" s="3">
         <v>27792300</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>14127400</v>
+        <v>11908500</v>
       </c>
       <c r="E47" s="3">
-        <v>15591700</v>
+        <v>13224700</v>
       </c>
       <c r="F47" s="3">
-        <v>9228500</v>
+        <v>7105100</v>
       </c>
       <c r="G47" s="3">
-        <v>7989100</v>
+        <v>6566900</v>
       </c>
       <c r="H47" s="3">
-        <v>9265100</v>
+        <v>7278000</v>
       </c>
       <c r="I47" s="3">
-        <v>11067100</v>
+        <v>5411900</v>
       </c>
       <c r="J47" s="3">
-        <v>10819000</v>
+        <v>7074000</v>
       </c>
       <c r="K47" s="3">
         <v>12149700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31565500</v>
+        <v>30746600</v>
       </c>
       <c r="E48" s="3">
-        <v>42079900</v>
+        <v>41277700</v>
       </c>
       <c r="F48" s="3">
-        <v>45194500</v>
+        <v>45327700</v>
       </c>
       <c r="G48" s="3">
-        <v>45680700</v>
+        <v>48407300</v>
       </c>
       <c r="H48" s="3">
-        <v>44429200</v>
+        <v>44080200</v>
       </c>
       <c r="I48" s="3">
-        <v>30383700</v>
+        <v>30787900</v>
       </c>
       <c r="J48" s="3">
-        <v>31372800</v>
+        <v>34895900</v>
       </c>
       <c r="K48" s="3">
         <v>32865000</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>43032500</v>
+        <v>41916100</v>
       </c>
       <c r="E49" s="3">
-        <v>52286500</v>
+        <v>51289700</v>
       </c>
       <c r="F49" s="3">
-        <v>58973100</v>
+        <v>59146900</v>
       </c>
       <c r="G49" s="3">
-        <v>59310900</v>
+        <v>62850900</v>
       </c>
       <c r="H49" s="3">
-        <v>59820400</v>
+        <v>59350500</v>
       </c>
       <c r="I49" s="3">
-        <v>45417100</v>
+        <v>46021300</v>
       </c>
       <c r="J49" s="3">
-        <v>47911500</v>
+        <v>53291900</v>
       </c>
       <c r="K49" s="3">
         <v>50292000</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>48436500</v>
+        <v>4946600</v>
       </c>
       <c r="E52" s="3">
-        <v>28335700</v>
+        <v>6880700</v>
       </c>
       <c r="F52" s="3">
-        <v>27745400</v>
+        <v>5597600</v>
       </c>
       <c r="G52" s="3">
-        <v>28847400</v>
+        <v>3867400</v>
       </c>
       <c r="H52" s="3">
-        <v>35925000</v>
+        <v>10247300</v>
       </c>
       <c r="I52" s="3">
-        <v>27264700</v>
+        <v>4469100</v>
       </c>
       <c r="J52" s="3">
-        <v>44448000</v>
+        <v>4127100</v>
       </c>
       <c r="K52" s="3">
         <v>45212700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>159882000</v>
+        <v>155734200</v>
       </c>
       <c r="E54" s="3">
-        <v>172255000</v>
+        <v>168971100</v>
       </c>
       <c r="F54" s="3">
-        <v>170625000</v>
+        <v>171127500</v>
       </c>
       <c r="G54" s="3">
-        <v>171748000</v>
+        <v>181998800</v>
       </c>
       <c r="H54" s="3">
-        <v>186263000</v>
+        <v>184800000</v>
       </c>
       <c r="I54" s="3">
-        <v>158234000</v>
+        <v>160338900</v>
       </c>
       <c r="J54" s="3">
-        <v>161279000</v>
+        <v>179390200</v>
       </c>
       <c r="K54" s="3">
         <v>168312000</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6653400</v>
+        <v>6429000</v>
       </c>
       <c r="E57" s="3">
-        <v>8850800</v>
+        <v>8613600</v>
       </c>
       <c r="F57" s="3">
-        <v>8159700</v>
+        <v>8183700</v>
       </c>
       <c r="G57" s="3">
-        <v>7504000</v>
+        <v>7951900</v>
       </c>
       <c r="H57" s="3">
-        <v>7473000</v>
+        <v>7414300</v>
       </c>
       <c r="I57" s="3">
-        <v>7273600</v>
+        <v>7370400</v>
       </c>
       <c r="J57" s="3">
-        <v>6880400</v>
+        <v>7653100</v>
       </c>
       <c r="K57" s="3">
         <v>6774500</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9590700</v>
+        <v>9402300</v>
       </c>
       <c r="E58" s="3">
-        <v>16305000</v>
+        <v>16853500</v>
       </c>
       <c r="F58" s="3">
-        <v>13248000</v>
+        <v>14020200</v>
       </c>
       <c r="G58" s="3">
-        <v>9401300</v>
+        <v>10646700</v>
       </c>
       <c r="H58" s="3">
-        <v>13264600</v>
+        <v>15840700</v>
       </c>
       <c r="I58" s="3">
-        <v>4729500</v>
+        <v>7445600</v>
       </c>
       <c r="J58" s="3">
-        <v>11464800</v>
+        <v>13060200</v>
       </c>
       <c r="K58" s="3">
         <v>13112700</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>9544200</v>
+        <v>11387400</v>
       </c>
       <c r="E59" s="3">
-        <v>13149400</v>
+        <v>5708400</v>
       </c>
       <c r="F59" s="3">
-        <v>15859700</v>
+        <v>7762700</v>
       </c>
       <c r="G59" s="3">
-        <v>14895000</v>
+        <v>7417800</v>
       </c>
       <c r="H59" s="3">
-        <v>16239600</v>
+        <v>6550500</v>
       </c>
       <c r="I59" s="3">
-        <v>16266200</v>
+        <v>5593700</v>
       </c>
       <c r="J59" s="3">
-        <v>24877800</v>
+        <v>19040300</v>
       </c>
       <c r="K59" s="3">
         <v>26236300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>25788300</v>
+        <v>32582800</v>
       </c>
       <c r="E60" s="3">
-        <v>38305200</v>
+        <v>37575000</v>
       </c>
       <c r="F60" s="3">
-        <v>37267400</v>
+        <v>37377200</v>
       </c>
       <c r="G60" s="3">
-        <v>31800300</v>
+        <v>33698400</v>
       </c>
       <c r="H60" s="3">
-        <v>36977200</v>
+        <v>36686800</v>
       </c>
       <c r="I60" s="3">
-        <v>28269300</v>
+        <v>28645300</v>
       </c>
       <c r="J60" s="3">
-        <v>43223000</v>
+        <v>48076900</v>
       </c>
       <c r="K60" s="3">
         <v>46123500</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>53528100</v>
+        <v>53723200</v>
       </c>
       <c r="E61" s="3">
-        <v>57228600</v>
+        <v>57350100</v>
       </c>
       <c r="F61" s="3">
-        <v>64385900</v>
+        <v>66248600</v>
       </c>
       <c r="G61" s="3">
-        <v>65649700</v>
+        <v>74167800</v>
       </c>
       <c r="H61" s="3">
-        <v>69722300</v>
+        <v>73764800</v>
       </c>
       <c r="I61" s="3">
-        <v>53923500</v>
+        <v>56800200</v>
       </c>
       <c r="J61" s="3">
-        <v>36141000</v>
+        <v>43169900</v>
       </c>
       <c r="K61" s="3">
         <v>37232600</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5342000</v>
+        <v>2300100</v>
       </c>
       <c r="E62" s="3">
-        <v>5299900</v>
+        <v>2325100</v>
       </c>
       <c r="F62" s="3">
-        <v>5757300</v>
+        <v>2622800</v>
       </c>
       <c r="G62" s="3">
-        <v>10260800</v>
+        <v>2603300</v>
       </c>
       <c r="H62" s="3">
-        <v>10199900</v>
+        <v>2064800</v>
       </c>
       <c r="I62" s="3">
-        <v>5769500</v>
+        <v>1887800</v>
       </c>
       <c r="J62" s="3">
-        <v>5925700</v>
+        <v>1894800</v>
       </c>
       <c r="K62" s="3">
         <v>4741900</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>93463700</v>
+        <v>89925600</v>
       </c>
       <c r="E66" s="3">
-        <v>102034000</v>
+        <v>98911300</v>
       </c>
       <c r="F66" s="3">
-        <v>109947000</v>
+        <v>107727200</v>
       </c>
       <c r="G66" s="3">
-        <v>109939000</v>
+        <v>114139700</v>
       </c>
       <c r="H66" s="3">
-        <v>118245000</v>
+        <v>115981300</v>
       </c>
       <c r="I66" s="3">
-        <v>89321300</v>
+        <v>89132400</v>
       </c>
       <c r="J66" s="3">
-        <v>86360700</v>
+        <v>94867600</v>
       </c>
       <c r="K66" s="3">
         <v>89750800</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>66418300</v>
+        <v>64695200</v>
       </c>
       <c r="E76" s="3">
-        <v>70220700</v>
+        <v>68882000</v>
       </c>
       <c r="F76" s="3">
-        <v>60677700</v>
+        <v>60856500</v>
       </c>
       <c r="G76" s="3">
-        <v>61808500</v>
+        <v>65497700</v>
       </c>
       <c r="H76" s="3">
-        <v>68017700</v>
+        <v>67483500</v>
       </c>
       <c r="I76" s="3">
-        <v>68912700</v>
+        <v>69829400</v>
       </c>
       <c r="J76" s="3">
-        <v>74918100</v>
+        <v>83331300</v>
       </c>
       <c r="K76" s="3">
         <v>78560800</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1262700</v>
+        <v>1229900</v>
       </c>
       <c r="E81" s="3">
-        <v>13111800</v>
+        <v>12861800</v>
       </c>
       <c r="F81" s="3">
-        <v>2477700</v>
+        <v>2485000</v>
       </c>
       <c r="G81" s="3">
-        <v>65300</v>
+        <v>69200</v>
       </c>
       <c r="H81" s="3">
-        <v>-1019000</v>
+        <v>-1011000</v>
       </c>
       <c r="I81" s="3">
-        <v>-8883000</v>
+        <v>-9001100</v>
       </c>
       <c r="J81" s="3">
-        <v>2701400</v>
+        <v>3004800</v>
       </c>
       <c r="K81" s="3">
         <v>-6851800</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11534500</v>
+        <v>7428000</v>
       </c>
       <c r="E83" s="3">
-        <v>15083300</v>
+        <v>7412000</v>
       </c>
       <c r="F83" s="3">
-        <v>15334700</v>
+        <v>7767200</v>
       </c>
       <c r="G83" s="3">
-        <v>15618300</v>
+        <v>11361500</v>
       </c>
       <c r="H83" s="3">
-        <v>15699100</v>
+        <v>10675800</v>
       </c>
       <c r="I83" s="3">
-        <v>10848900</v>
+        <v>6570100</v>
       </c>
       <c r="J83" s="3">
-        <v>11529000</v>
+        <v>7404200</v>
       </c>
       <c r="K83" s="3">
         <v>12062700</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>18338500</v>
+        <v>17862800</v>
       </c>
       <c r="E89" s="3">
-        <v>19996600</v>
+        <v>19615400</v>
       </c>
       <c r="F89" s="3">
-        <v>20026500</v>
+        <v>20085500</v>
       </c>
       <c r="G89" s="3">
-        <v>19067300</v>
+        <v>20205400</v>
       </c>
       <c r="H89" s="3">
-        <v>19249000</v>
+        <v>19097800</v>
       </c>
       <c r="I89" s="3">
-        <v>14376600</v>
+        <v>14567900</v>
       </c>
       <c r="J89" s="3">
-        <v>15063400</v>
+        <v>16755000</v>
       </c>
       <c r="K89" s="3">
         <v>15476000</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4673000</v>
+        <v>-4551700</v>
       </c>
       <c r="E91" s="3">
-        <v>-6922500</v>
+        <v>-5385700</v>
       </c>
       <c r="F91" s="3">
-        <v>-6421900</v>
+        <v>-5051100</v>
       </c>
       <c r="G91" s="3">
-        <v>-5995400</v>
+        <v>-6353300</v>
       </c>
       <c r="H91" s="3">
-        <v>-5739600</v>
+        <v>-5694500</v>
       </c>
       <c r="I91" s="3">
-        <v>-5596700</v>
+        <v>-5671200</v>
       </c>
       <c r="J91" s="3">
-        <v>-5446100</v>
+        <v>-6057700</v>
       </c>
       <c r="K91" s="3">
         <v>-6838700</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6780700</v>
+        <v>-6604800</v>
       </c>
       <c r="E94" s="3">
-        <v>-419800</v>
+        <v>-411800</v>
       </c>
       <c r="F94" s="3">
-        <v>-7607000</v>
+        <v>-7629400</v>
       </c>
       <c r="G94" s="3">
-        <v>-10258600</v>
+        <v>-10870900</v>
       </c>
       <c r="H94" s="3">
-        <v>-8958300</v>
+        <v>-8887900</v>
       </c>
       <c r="I94" s="3">
-        <v>-10208700</v>
+        <v>-10344600</v>
       </c>
       <c r="J94" s="3">
-        <v>-10899900</v>
+        <v>-12123900</v>
       </c>
       <c r="K94" s="3">
         <v>-9165100</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2691500</v>
+        <v>2621600</v>
       </c>
       <c r="E96" s="3">
-        <v>-2751300</v>
+        <v>2698800</v>
       </c>
       <c r="F96" s="3">
-        <v>-2740200</v>
+        <v>2748300</v>
       </c>
       <c r="G96" s="3">
-        <v>-2688100</v>
+        <v>2848600</v>
       </c>
       <c r="H96" s="3">
-        <v>-2543000</v>
+        <v>2523100</v>
       </c>
       <c r="I96" s="3">
-        <v>-4501300</v>
+        <v>4561200</v>
       </c>
       <c r="J96" s="3">
-        <v>-4341800</v>
+        <v>4829400</v>
       </c>
       <c r="K96" s="3">
         <v>-4041200</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-17561000</v>
+        <v>-17105400</v>
       </c>
       <c r="E100" s="3">
-        <v>-14875100</v>
+        <v>-14591500</v>
       </c>
       <c r="F100" s="3">
-        <v>-10750400</v>
+        <v>-10782000</v>
       </c>
       <c r="G100" s="3">
-        <v>-16831100</v>
+        <v>-17835700</v>
       </c>
       <c r="H100" s="3">
-        <v>-10358300</v>
+        <v>-10276900</v>
       </c>
       <c r="I100" s="3">
-        <v>4914400</v>
+        <v>4979800</v>
       </c>
       <c r="J100" s="3">
-        <v>-8012400</v>
+        <v>-8912200</v>
       </c>
       <c r="K100" s="3">
         <v>-9897400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-104100</v>
+        <v>-101400</v>
       </c>
       <c r="E101" s="3">
-        <v>13300</v>
+        <v>13000</v>
       </c>
       <c r="F101" s="3">
-        <v>82000</v>
+        <v>82200</v>
       </c>
       <c r="G101" s="3">
-        <v>-282400</v>
+        <v>-299300</v>
       </c>
       <c r="H101" s="3">
-        <v>-283500</v>
+        <v>-281300</v>
       </c>
       <c r="I101" s="3">
-        <v>12200</v>
+        <v>12300</v>
       </c>
       <c r="J101" s="3">
-        <v>-479600</v>
+        <v>-533400</v>
       </c>
       <c r="K101" s="3">
         <v>-340600</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-6107300</v>
+        <v>-5948900</v>
       </c>
       <c r="E102" s="3">
-        <v>4715100</v>
+        <v>4625200</v>
       </c>
       <c r="F102" s="3">
-        <v>1751100</v>
+        <v>1756300</v>
       </c>
       <c r="G102" s="3">
-        <v>-8304800</v>
+        <v>-8800500</v>
       </c>
       <c r="H102" s="3">
-        <v>-351100</v>
+        <v>-348400</v>
       </c>
       <c r="I102" s="3">
-        <v>9094500</v>
+        <v>9215500</v>
       </c>
       <c r="J102" s="3">
-        <v>-4328500</v>
+        <v>-4814600</v>
       </c>
       <c r="K102" s="3">
         <v>-3927000</v>

--- a/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>VOD</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>40475600</v>
+      </c>
+      <c r="E8" s="3">
         <v>39612700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>40930000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41113100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>51419000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>49422000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49007900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>57374600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>51827300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>53640400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>50218800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>46973500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42134200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>43556800</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>26944400</v>
+      </c>
+      <c r="E9" s="3">
         <v>26388000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26465700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26603000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35312200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>33716500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>33849600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>40373300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>37622100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>39536200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36402300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>34228700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29425600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30519200</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13531100</v>
+      </c>
+      <c r="E10" s="3">
         <v>13224700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>14464400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14510100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>16106800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15705500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15158200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>17001400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>14205100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14104200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13816500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12744800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12708600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13037500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,81 +979,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4880000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-457400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-10088000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-50000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1566900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3207700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3956200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>650500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1387300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>612800</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>8084900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>8528500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4544100</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8180900</v>
+      </c>
+      <c r="E15" s="3">
         <v>5300500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5624700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8552500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11956600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11487900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10993300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12823700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>35906800</v>
+      </c>
+      <c r="E17" s="3">
         <v>35864700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36046300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35232200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47408500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>45439600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45098800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>51435300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47774100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>52218900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48067200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>51766900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>44573100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37253400</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4568700</v>
+      </c>
+      <c r="E18" s="3">
         <v>3748000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4883700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5880900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4010600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3982400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3909100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5939400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4053200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1421500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2151600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4793400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2438900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6303300</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E20" s="3">
         <v>545900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1041900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-468800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1671400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>4191200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1717200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-45600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>280700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-596600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1216400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-283000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2137700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2065600</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>12615700</v>
+      </c>
+      <c r="E21" s="3">
         <v>8502500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11550400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>14902200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17638500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>11279100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13185200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18808700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16468500</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15043600</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>15928000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2086000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2538600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2061100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2069500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2434300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2397800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1654300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1414300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1295900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1029500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1568300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1379300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3556500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3719400</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1597500</v>
+      </c>
+      <c r="E23" s="3">
         <v>1747800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14204700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4609000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5102100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>873600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2932700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4777600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3038000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-204600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1799700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-6455700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3857800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4649500</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2427600</v>
+      </c>
+      <c r="E24" s="3">
         <v>53900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>534600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1734100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4535200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1373600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1679000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1082900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5183700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5316700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-6301100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-20312800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>527200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>791000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4025100</v>
+      </c>
+      <c r="E26" s="3">
         <v>1693800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13670100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2874900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>566900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-500000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4611700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5860500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2145700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5521300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8100800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13857100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4385000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3858500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4506100</v>
+      </c>
+      <c r="E27" s="3">
         <v>1229900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12861800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2485000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>69300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1011000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9001100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3004800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2382900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5826000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7895300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13653700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4655200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3806900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,54 +1640,60 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E29" s="3">
         <v>-70100</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-268400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>205500</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-3967500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-2425800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-4468800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>5400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-281300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>58931800</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>5112700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>3988700</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-134000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-545900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1041900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>468800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1671400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-4191200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1717200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>45600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-280700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>596600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1216400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>283000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2137700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2065600</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4506100</v>
+      </c>
+      <c r="E33" s="3">
         <v>1229900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12861800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2485000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>69200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1011000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9001100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3004800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6851800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5820600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7614000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>72585600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>457400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7795600</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4506100</v>
+      </c>
+      <c r="E35" s="3">
         <v>1229900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12861800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2485000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>69200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1011000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9001100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3004800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6851800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5820600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7614000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>72585600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>457400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7795600</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,413 +2072,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11890400</v>
+      </c>
+      <c r="E41" s="3">
         <v>6670600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12717300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8327000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6832200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14897800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>15305300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5758300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9613400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24153800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14844000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>18717800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8357900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8008800</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>8024200</v>
+      </c>
+      <c r="E42" s="3">
         <v>4694100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>7364200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>8034900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7103300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6564800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13275000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9812700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6659200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>9425000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7715700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>11523500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8970500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1484400</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10352400</v>
+      </c>
+      <c r="E43" s="3">
         <v>7213300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8904800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9586800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10178400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9894500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11111100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10778600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8926800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>18023000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>17585100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>11390000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5397000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8098500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>666900</v>
+      </c>
+      <c r="E44" s="3">
         <v>612800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1038700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>928700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>793400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>657100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>801300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>715800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>626700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1542100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1192500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1080400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>891200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>545300</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>22841700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2381600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2789400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7003500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3019800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2558900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18270300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1966200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6462500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3161400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>526700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3942000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4330900</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>30933900</v>
+      </c>
+      <c r="E46" s="3">
         <v>42679900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>33313800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>30635400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33180800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>36081300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>44428700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>46755000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>27792300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34394000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>28497600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>30284200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>24026100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>22467800</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10857100</v>
+      </c>
+      <c r="E47" s="3">
         <v>11908500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>13224700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7105100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>6566900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7278000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5411900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7074000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12149700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11741400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>13054700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8497800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>62541700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>44185100</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>33195000</v>
+      </c>
+      <c r="E48" s="3">
         <v>30746600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41277700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45327700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>48407300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44080200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30787900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34895900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32865000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>76492200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>65812200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>55984500</v>
       </c>
-      <c r="O48" s="3" t="s">
+      <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20930700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>36141400</v>
+      </c>
+      <c r="E49" s="3">
         <v>41916100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>51289700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>59146900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>62850900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>59350500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>46021300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>53291900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>50292000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>126135000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>106907000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>114385000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>107136000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>66774100</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>261600</v>
+      </c>
+      <c r="E52" s="3">
         <v>4946600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6880700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5597600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3867400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10247300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4469100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4127100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>45212700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>34662200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>34484200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25286200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3218400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2245100</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>138911600</v>
+      </c>
+      <c r="E54" s="3">
         <v>155734200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>168971100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>171127500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>181998800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>184800000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>160338900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>179390200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>168312000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>182111000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>176006000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>149253000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>153512000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>156603000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15200000</v>
+      </c>
+      <c r="E57" s="3">
         <v>6429000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>8613600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8183700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>7951900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7414300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7370400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7653100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6774500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8062800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>26700000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5832200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>9059300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5098300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7616700</v>
+      </c>
+      <c r="E58" s="3">
         <v>9402300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16853500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14020200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>10646700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15840700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7445600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>13060200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13112700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>29470400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27216900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5211100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14101100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5886000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1776900</v>
+      </c>
+      <c r="E59" s="3">
         <v>11387400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5708400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7762700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7417800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6550500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5593700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19040300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26236300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20263000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16151800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24224200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17625800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15971500</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>24593600</v>
+      </c>
+      <c r="E60" s="3">
         <v>32582800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>37575000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37377200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>33698400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36686800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28645300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>48076900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>46123500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>45482900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41494200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30672500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>31483900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26955800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>49822700</v>
+      </c>
+      <c r="E61" s="3">
         <v>53723200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>57350100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>66248600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>74167800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>73764800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>56800200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>43169900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>37232600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>39621300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>32215400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>26146200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>30132200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31821900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5155600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2325100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2622800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2603300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2064800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1887800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1894800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4741900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7369200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6486900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6150700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13106700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10083300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>80636600</v>
+      </c>
+      <c r="E66" s="3">
         <v>89925600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>98911300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>107727200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>114139700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>115981300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>89132400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>94867600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>89750800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>92378600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>81027800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>62521000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>74186800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>70282600</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,9 +3473,12 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3336,21 +3509,24 @@
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>-89136900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-62998800</v>
       </c>
-      <c r="O72" s="3" t="s">
+      <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-94206800</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>57009300</v>
+      </c>
+      <c r="E76" s="3">
         <v>64695200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>68882000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>60856500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>65497700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>67483500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>69829400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>83331300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>78560800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>89732700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>94978200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>86731700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>79325200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>86320300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4506100</v>
+      </c>
+      <c r="E81" s="3">
         <v>1229900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12861800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2485000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>69200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1011000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9001100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3004800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6851800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5820600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7614000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>72585600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>457400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7795600</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7651300</v>
+      </c>
+      <c r="E83" s="3">
         <v>7428000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7412000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7767200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11361500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>10675800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6570100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7404200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12062700</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11529000</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="3">
         <v>7540900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16615900</v>
+      </c>
+      <c r="E89" s="3">
         <v>17862800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>19615400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20085500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20205400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>19097800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>14567900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>16755000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>15476000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>13642200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13148100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7628000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9773500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11553100</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4673600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4551700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5385700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5051100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6353300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5694500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5671200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6057700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6838700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7887200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7601600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5385100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4383900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4567600</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5143800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6604800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-411800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7629400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10870900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8887900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10344600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12123900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9165100</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13735600</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="3">
         <v>7383800</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1931500</v>
+      </c>
+      <c r="E96" s="3">
         <v>2621600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2698800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2748300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2848600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2523100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>4561200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4829400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-4041200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-4047000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-3900400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-6218000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-5323100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-7453400</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-16513200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17105400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14591500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10782000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17835700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-10276900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4979800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8912200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9897400</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3281800</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-17580500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-81100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-101400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>13000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>82200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-299300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-281300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>12300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-533400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-340600</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1012000</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-388200</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5165400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5948900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4625200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1756300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8800500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-348400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9215500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4814600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-3927000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2964700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2857300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3192300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>559300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>968300</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
@@ -989,13 +989,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>4880000</v>
+        <v>3959100</v>
       </c>
       <c r="E14" s="3">
         <v>-457400</v>
       </c>
       <c r="F14" s="3">
-        <v>-10088000</v>
+        <v>-10303100</v>
       </c>
       <c r="G14" s="3">
         <v>-50000</v>
@@ -1037,13 +1037,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>8180900</v>
+        <v>5553400</v>
       </c>
       <c r="E15" s="3">
-        <v>5300500</v>
+        <v>7980400</v>
       </c>
       <c r="F15" s="3">
-        <v>5624700</v>
+        <v>8172500</v>
       </c>
       <c r="G15" s="3">
         <v>8552500</v>
@@ -1102,13 +1102,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>35906800</v>
+        <v>36827700</v>
       </c>
       <c r="E17" s="3">
-        <v>35864700</v>
+        <v>36012500</v>
       </c>
       <c r="F17" s="3">
-        <v>36046300</v>
+        <v>36002800</v>
       </c>
       <c r="G17" s="3">
         <v>35232200</v>
@@ -1150,13 +1150,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4568700</v>
+        <v>3647900</v>
       </c>
       <c r="E18" s="3">
-        <v>3748000</v>
+        <v>3600200</v>
       </c>
       <c r="F18" s="3">
-        <v>4883700</v>
+        <v>4927200</v>
       </c>
       <c r="G18" s="3">
         <v>5880900</v>
@@ -1218,13 +1218,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>134000</v>
+        <v>131900</v>
       </c>
       <c r="E20" s="3">
-        <v>545900</v>
+        <v>398100</v>
       </c>
       <c r="F20" s="3">
-        <v>-1041900</v>
+        <v>-783400</v>
       </c>
       <c r="G20" s="3">
         <v>-468800</v>
@@ -1266,13 +1266,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12615700</v>
+        <v>9069400</v>
       </c>
       <c r="E21" s="3">
-        <v>8502500</v>
+        <v>11182400</v>
       </c>
       <c r="F21" s="3">
-        <v>11550400</v>
+        <v>13883100</v>
       </c>
       <c r="G21" s="3">
         <v>14902200</v>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>2086000</v>
+        <v>2088200</v>
       </c>
       <c r="E22" s="3">
         <v>2538600</v>
@@ -1794,13 +1794,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-134000</v>
+        <v>-131900</v>
       </c>
       <c r="E32" s="3">
-        <v>-545900</v>
+        <v>-398100</v>
       </c>
       <c r="F32" s="3">
-        <v>1041900</v>
+        <v>783400</v>
       </c>
       <c r="G32" s="3">
         <v>468800</v>
@@ -2127,13 +2127,13 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8024200</v>
+        <v>6932600</v>
       </c>
       <c r="E42" s="3">
         <v>4694100</v>
       </c>
       <c r="F42" s="3">
-        <v>7364200</v>
+        <v>7623900</v>
       </c>
       <c r="G42" s="3">
         <v>8034900</v>
@@ -2175,13 +2175,13 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10352400</v>
+        <v>8091200</v>
       </c>
       <c r="E43" s="3">
         <v>7213300</v>
       </c>
       <c r="F43" s="3">
-        <v>8904800</v>
+        <v>11933900</v>
       </c>
       <c r="G43" s="3">
         <v>9586800</v>
@@ -2270,14 +2270,14 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>2589700</v>
       </c>
       <c r="E45" s="3">
         <v>22841700</v>
       </c>
-      <c r="F45" s="3">
-        <v>2381600</v>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G45" s="3">
         <v>2789400</v>
@@ -2607,13 +2607,13 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>261600</v>
+        <v>5067000</v>
       </c>
       <c r="E52" s="3">
         <v>4946600</v>
       </c>
       <c r="F52" s="3">
-        <v>6880700</v>
+        <v>357500</v>
       </c>
       <c r="G52" s="3">
         <v>5597600</v>
@@ -2791,13 +2791,13 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>15200000</v>
+        <v>7013600</v>
       </c>
       <c r="E57" s="3">
         <v>6429000</v>
       </c>
       <c r="F57" s="3">
-        <v>8613600</v>
+        <v>19825100</v>
       </c>
       <c r="G57" s="3">
         <v>8183700</v>
@@ -2839,13 +2839,13 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7616700</v>
+        <v>7705400</v>
       </c>
       <c r="E58" s="3">
-        <v>9402300</v>
+        <v>8397900</v>
       </c>
       <c r="F58" s="3">
-        <v>16853500</v>
+        <v>14334000</v>
       </c>
       <c r="G58" s="3">
         <v>14020200</v>
@@ -2887,13 +2887,13 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1776900</v>
+        <v>4572000</v>
       </c>
       <c r="E59" s="3">
         <v>11387400</v>
       </c>
       <c r="F59" s="3">
-        <v>5708400</v>
+        <v>1228800</v>
       </c>
       <c r="G59" s="3">
         <v>7762700</v>
@@ -2938,10 +2938,10 @@
         <v>24593600</v>
       </c>
       <c r="E60" s="3">
-        <v>32582800</v>
+        <v>31578400</v>
       </c>
       <c r="F60" s="3">
-        <v>37575000</v>
+        <v>35387900</v>
       </c>
       <c r="G60" s="3">
         <v>37377200</v>
@@ -2983,13 +2983,13 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>49822700</v>
+        <v>51794200</v>
       </c>
       <c r="E61" s="3">
-        <v>53723200</v>
+        <v>54727600</v>
       </c>
       <c r="F61" s="3">
-        <v>57350100</v>
+        <v>58324600</v>
       </c>
       <c r="G61" s="3">
         <v>66248600</v>
@@ -3031,13 +3031,13 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5155600</v>
+        <v>2306500</v>
       </c>
       <c r="E62" s="3">
         <v>2300100</v>
       </c>
       <c r="F62" s="3">
-        <v>2325100</v>
+        <v>4080800</v>
       </c>
       <c r="G62" s="3">
         <v>2622800</v>
@@ -3892,13 +3892,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7651300</v>
+        <v>7683700</v>
       </c>
       <c r="E83" s="3">
-        <v>7428000</v>
+        <v>7443100</v>
       </c>
       <c r="F83" s="3">
-        <v>7412000</v>
+        <v>7469600</v>
       </c>
       <c r="G83" s="3">
         <v>7767200</v>

--- a/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VOD_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>VOD</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>46651700</v>
+      </c>
+      <c r="E8" s="3">
         <v>40475600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>39612700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>40930000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>41113100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>51419000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49422000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>49007900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>57374600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>51827300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>53640400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>50218800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>46973500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>42134200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>43556800</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>31970500</v>
+      </c>
+      <c r="E9" s="3">
         <v>26944400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>26388000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26465700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26603000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35312200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>33716500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>33849600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>40373300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>37622100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>39536200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36402300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>34228700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29425600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30519200</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14681200</v>
+      </c>
+      <c r="E10" s="3">
         <v>13531100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>13224700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14464400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14510100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>16106800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>15705500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15158200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>17001400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>14205100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>14104200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13816500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12744800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12708600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13037500</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,87 +998,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-88800</v>
+      </c>
+      <c r="E14" s="3">
         <v>3959100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-457400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-10303100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-50000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1566900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3207700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3956200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>650500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1387300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>612800</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>8084900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>8528500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4544100</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6686300</v>
+      </c>
+      <c r="E15" s="3">
         <v>5553400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7980400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8172500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8552500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11956600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11487900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10993300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12823700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1078,9 +1100,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>43020900</v>
+      </c>
+      <c r="E17" s="3">
         <v>36827700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36012500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36002800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35232200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47408500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>45439600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>45098800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51435300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47774100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>52218900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>48067200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51766900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>44573100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37253400</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3630800</v>
+      </c>
+      <c r="E18" s="3">
         <v>3647900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3600200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4927200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5880900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4010600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3982400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3909100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5939400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4053200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1421500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2151600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4793400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2438900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6303300</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>626100</v>
+      </c>
+      <c r="E20" s="3">
         <v>131900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>398100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-783400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-468800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1671400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>4191200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1717200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-45600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>280700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-596600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1216400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-283000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2137700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2065600</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>9691000</v>
+      </c>
+      <c r="E21" s="3">
         <v>9069400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11182400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13883100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14902200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17638500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>11279100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13185200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18808700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16468500</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15043600</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>15928000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2552700</v>
+      </c>
+      <c r="E22" s="3">
         <v>2088200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2538600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2061100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2069500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2434300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2397800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1654300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1414300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1295900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1029500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1568300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1379300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3556500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3719400</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2149200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1597500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1747800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14204700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4609000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5102100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>873600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2932700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4777600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3038000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-204600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1799700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-6455700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3857800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4649500</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2081200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2427600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>53900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>534600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1734100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4535200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1373600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1679000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1082900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5183700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5316700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6301100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-20312800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>527200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>791000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4025100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1693800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13670100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2874900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>566900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4611700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5860500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2145700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5521300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8100800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13857100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-4385000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3858500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-457700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4506100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1229900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12861800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2485000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>69300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1011000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9001100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3004800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2382900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5826000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7895300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13653700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-4655200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3806900</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,57 +1700,63 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-124500</v>
+      </c>
+      <c r="E29" s="3">
         <v>-23800</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-70100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-268400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>205500</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
       <c r="I29" s="3">
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>-3967500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-2425800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-4468800</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>5400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-281300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>58931800</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>5112700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>3988700</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-626100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-131900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-398100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>783400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>468800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1671400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-4191200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1717200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>45600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-280700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>596600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1216400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>283000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2137700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2065600</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-457700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4506100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1229900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12861800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2485000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>69200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1011000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9001100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3004800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6851800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5820600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7614000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>72585600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>457400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7795600</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-457700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4506100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1229900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12861800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2485000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>69200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1011000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9001100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3004800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6851800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5820600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7614000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>72585600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>457400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7795600</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,440 +2158,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10356300</v>
+      </c>
+      <c r="E41" s="3">
         <v>11890400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6670600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12717300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8327000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6832200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14897800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15305300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5758300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9613400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24153800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14844000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>18717800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8357900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8008800</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6458000</v>
+      </c>
+      <c r="E42" s="3">
         <v>6932600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4694100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>7623900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8034900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7103300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6564800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13275000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>9812700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6659200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>9425000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7715700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>11523500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8970500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1484400</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9551500</v>
+      </c>
+      <c r="E43" s="3">
         <v>8091200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7213300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11933900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9586800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10178400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>9894500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11111100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10778600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8926800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>18023000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>17585100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>11390000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5397000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>8098500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>687200</v>
+      </c>
+      <c r="E44" s="3">
         <v>666900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>612800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1038700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>928700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>793400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>657100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>801300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>715800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>626700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1542100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1192500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1080400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>891200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>545300</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3302200</v>
+      </c>
+      <c r="E45" s="3">
         <v>2589700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22841700</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2789400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7003500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3019800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2558900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18270300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1966200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6462500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3161400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>526700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3942000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4330900</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>31467800</v>
+      </c>
+      <c r="E46" s="3">
         <v>30933900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42679900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>33313800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>30635400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33180800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36081300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44428700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>46755000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>27792300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34394000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>28497600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>30284200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>24026100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>22467800</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9891600</v>
+      </c>
+      <c r="E47" s="3">
         <v>10857100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11908500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13224700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7105100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>6566900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7278000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5411900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7074000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>12149700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11741400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13054700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8497800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>62541700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>44185100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39424700</v>
+      </c>
+      <c r="E48" s="3">
         <v>33195000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30746600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41277700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45327700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>48407300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44080200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30787900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34895900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32865000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>76492200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>65812200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>55984500</v>
       </c>
-      <c r="P48" s="3" t="s">
+      <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20930700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>41827500</v>
+      </c>
+      <c r="E49" s="3">
         <v>36141400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>41916100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>51289700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>59146900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>62850900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>59350500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>46021300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>53291900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>50292000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>126135000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>106907000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>114385000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>107136000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>66774100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4168100</v>
+      </c>
+      <c r="E52" s="3">
         <v>5067000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4946600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>357500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5597600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>3867400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10247300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4469100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4127100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>45212700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>34662200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>34484200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25286200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3218400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2245100</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>149795900</v>
+      </c>
+      <c r="E54" s="3">
         <v>138911600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>155734200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>168971100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>171127500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>181998800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>184800000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>160338900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>179390200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>168312000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>182111000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>176006000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>149253000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>153512000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>156603000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7514100</v>
+      </c>
+      <c r="E57" s="3">
         <v>7013600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6429000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19825100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8183700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>7951900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7414300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7370400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7653100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6774500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8062800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26700000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5832200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>9059300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5098300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8328100</v>
+      </c>
+      <c r="E58" s="3">
         <v>7705400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8397900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14334000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>14020200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10646700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>15840700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7445600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>13060200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>13112700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>29470400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27216900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5211100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14101100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5886000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4572000</v>
+        <v>4924500</v>
       </c>
       <c r="E59" s="3">
+        <v>4429300</v>
+      </c>
+      <c r="F59" s="3">
         <v>11387400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1228800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7762700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7417800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6550500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5593700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>19040300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26236300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20263000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16151800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24224200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17625800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15971500</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>27666300</v>
+      </c>
+      <c r="E60" s="3">
         <v>24593600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31578400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>35387900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37377200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>33698400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36686800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28645300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>48076900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46123500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45482900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41494200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30672500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>31483900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>26955800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>54450600</v>
+      </c>
+      <c r="E61" s="3">
         <v>51794200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>54727600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>58324600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>66248600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>74167800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>73764800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>56800200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>43169900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37232600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>39621300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>32215400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>26146200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>30132200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31821900</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2613900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2306500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4080800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2622800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2603300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2064800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1887800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1894800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4741900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7369200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6486900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6150700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13106700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10083300</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87112900</v>
+      </c>
+      <c r="E66" s="3">
         <v>80636600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>89925600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>98911300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>107727200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>114139700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>115981300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>89132400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>94867600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>89750800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>92378600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>81027800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>62521000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>74186800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>70282600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,9 +3646,12 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3512,21 +3685,24 @@
       <c r="M72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O72" s="3">
         <v>-89136900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-62998800</v>
       </c>
-      <c r="P72" s="3" t="s">
+      <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-94206800</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>58380000</v>
+      </c>
+      <c r="E76" s="3">
         <v>57009300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64695200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>68882000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>60856500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>65497700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>67483500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>69829400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>83331300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>78560800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>89732700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>94978200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>86731700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>79325200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>86320300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-457700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4506100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1229900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12861800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2485000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>69200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1011000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9001100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3004800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6851800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5820600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7614000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>72585600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>457400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7795600</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7683700</v>
+        <v>9299000</v>
       </c>
       <c r="E83" s="3">
+        <v>7651300</v>
+      </c>
+      <c r="F83" s="3">
         <v>7443100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7469600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7767200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>11361500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10675800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6570100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7404200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12062700</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11529000</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>7540900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16477600</v>
+      </c>
+      <c r="E89" s="3">
         <v>16615900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17862800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>19615400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20085500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20205400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>19097800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>14567900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16755000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>15476000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>13642200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>13148100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7628000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9773500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11553100</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5616300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4673600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4551700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5385700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-5051100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-6353300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5694500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5671200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6057700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6838700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7887200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7601600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5385100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4383900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4567600</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4886400</v>
+      </c>
+      <c r="E94" s="3">
         <v>5143800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6604800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-411800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7629400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10870900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8887900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10344600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-12123900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9165100</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13735600</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>7383800</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1260200</v>
+      </c>
+      <c r="E96" s="3">
         <v>1931500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2621600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2698800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2748300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2848600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2523100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>4561200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>4829400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-4041200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-4047000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-3900400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-6218000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-5323100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-7453400</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13612400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-16513200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17105400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14591500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-10782000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17835700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-10276900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4979800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8912200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9897400</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3281800</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>-17580500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-261700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-81100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-101400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>82200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-299300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-281300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>12300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-533400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-340600</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1012000</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>-388200</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2282900</v>
+      </c>
+      <c r="E102" s="3">
         <v>5165400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5948900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4625200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1756300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8800500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-348400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9215500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4814600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3927000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2964700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2857300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>3192300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>559300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>968300</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
